--- a/doc/AI-S4_portfoliomatrix.xlsx
+++ b/doc/AI-S4_portfoliomatrix.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mathi\Documents\hu\S4\ai-s4_student\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1114E1FE-A7D5-475E-969B-18F7DE9CB2CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E76CA1-AF12-49B2-9A5E-6872BB60F71D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{9145D055-8147-4D48-BED2-085A2CF38ACC}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="73">
   <si>
     <t>Leeruitkomsten</t>
   </si>
@@ -1414,6 +1414,132 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="14" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -1435,137 +1561,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2041,64 +2041,64 @@
         <v>70</v>
       </c>
       <c r="D4" s="13"/>
-      <c r="E4" s="116" t="s">
+      <c r="E4" s="82" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="114" t="s">
+      <c r="F4" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="114" t="s">
+      <c r="G4" s="80" t="s">
         <v>65</v>
       </c>
-      <c r="H4" s="114" t="s">
+      <c r="H4" s="80" t="s">
         <v>67</v>
       </c>
-      <c r="I4" s="114" t="s">
+      <c r="I4" s="80" t="s">
         <v>68</v>
       </c>
-      <c r="J4" s="114" t="s">
+      <c r="J4" s="80" t="s">
         <v>66</v>
       </c>
-      <c r="K4" s="114" t="s">
+      <c r="K4" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="L4" s="114" t="s">
+      <c r="L4" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="M4" s="114" t="s">
+      <c r="M4" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="N4" s="112" t="s">
+      <c r="N4" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="O4" s="104" t="s">
+      <c r="O4" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="P4" s="107" t="s">
+      <c r="P4" s="75" t="s">
         <v>29</v>
       </c>
-      <c r="Q4" s="107" t="s">
+      <c r="Q4" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="R4" s="107" t="s">
+      <c r="R4" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="S4" s="107" t="s">
+      <c r="S4" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="T4" s="107" t="s">
+      <c r="T4" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="U4" s="107" t="s">
+      <c r="U4" s="75" t="s">
         <v>58</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="75" t="s">
         <v>56</v>
       </c>
-      <c r="W4" s="107" t="s">
+      <c r="W4" s="75" t="s">
         <v>32</v>
       </c>
-      <c r="X4" s="101" t="s">
+      <c r="X4" s="86" t="s">
         <v>31</v>
       </c>
       <c r="Y4" s="9"/>
@@ -2113,26 +2113,26 @@
         <v>71</v>
       </c>
       <c r="D5" s="16"/>
-      <c r="E5" s="117"/>
-      <c r="F5" s="115"/>
-      <c r="G5" s="115"/>
-      <c r="H5" s="115"/>
-      <c r="I5" s="115"/>
-      <c r="J5" s="115"/>
-      <c r="K5" s="115"/>
-      <c r="L5" s="115"/>
-      <c r="M5" s="115"/>
-      <c r="N5" s="113"/>
-      <c r="O5" s="105"/>
-      <c r="P5" s="108"/>
-      <c r="Q5" s="108"/>
-      <c r="R5" s="108"/>
-      <c r="S5" s="108"/>
-      <c r="T5" s="108"/>
-      <c r="U5" s="108"/>
-      <c r="V5" s="108"/>
-      <c r="W5" s="108"/>
-      <c r="X5" s="102"/>
+      <c r="E5" s="83"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="81"/>
+      <c r="H5" s="81"/>
+      <c r="I5" s="81"/>
+      <c r="J5" s="81"/>
+      <c r="K5" s="81"/>
+      <c r="L5" s="81"/>
+      <c r="M5" s="81"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="76"/>
+      <c r="U5" s="76"/>
+      <c r="V5" s="76"/>
+      <c r="W5" s="76"/>
+      <c r="X5" s="87"/>
       <c r="Y5" s="9"/>
       <c r="Z5"/>
     </row>
@@ -2145,26 +2145,26 @@
         <v>1</v>
       </c>
       <c r="D6" s="16"/>
-      <c r="E6" s="117"/>
-      <c r="F6" s="115"/>
-      <c r="G6" s="115"/>
-      <c r="H6" s="115"/>
-      <c r="I6" s="115"/>
-      <c r="J6" s="115"/>
-      <c r="K6" s="115"/>
-      <c r="L6" s="115"/>
-      <c r="M6" s="115"/>
-      <c r="N6" s="113"/>
-      <c r="O6" s="105"/>
-      <c r="P6" s="108"/>
-      <c r="Q6" s="108"/>
-      <c r="R6" s="108"/>
-      <c r="S6" s="108"/>
-      <c r="T6" s="108"/>
-      <c r="U6" s="108"/>
-      <c r="V6" s="108"/>
-      <c r="W6" s="108"/>
-      <c r="X6" s="102"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="81"/>
+      <c r="H6" s="81"/>
+      <c r="I6" s="81"/>
+      <c r="J6" s="81"/>
+      <c r="K6" s="81"/>
+      <c r="L6" s="81"/>
+      <c r="M6" s="81"/>
+      <c r="N6" s="79"/>
+      <c r="O6" s="90"/>
+      <c r="P6" s="76"/>
+      <c r="Q6" s="76"/>
+      <c r="R6" s="76"/>
+      <c r="S6" s="76"/>
+      <c r="T6" s="76"/>
+      <c r="U6" s="76"/>
+      <c r="V6" s="76"/>
+      <c r="W6" s="76"/>
+      <c r="X6" s="87"/>
       <c r="Y6" s="9"/>
       <c r="Z6"/>
     </row>
@@ -2173,37 +2173,37 @@
       <c r="B7" s="2"/>
       <c r="C7" s="4"/>
       <c r="D7" s="5"/>
-      <c r="E7" s="117"/>
-      <c r="F7" s="115"/>
-      <c r="G7" s="115"/>
-      <c r="H7" s="115"/>
-      <c r="I7" s="115"/>
-      <c r="J7" s="115"/>
-      <c r="K7" s="115"/>
-      <c r="L7" s="115"/>
-      <c r="M7" s="115"/>
-      <c r="N7" s="113"/>
-      <c r="O7" s="106"/>
-      <c r="P7" s="109"/>
-      <c r="Q7" s="109"/>
-      <c r="R7" s="109"/>
-      <c r="S7" s="109"/>
-      <c r="T7" s="109"/>
-      <c r="U7" s="109"/>
-      <c r="V7" s="109"/>
-      <c r="W7" s="109"/>
-      <c r="X7" s="103"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="81"/>
+      <c r="H7" s="81"/>
+      <c r="I7" s="81"/>
+      <c r="J7" s="81"/>
+      <c r="K7" s="81"/>
+      <c r="L7" s="81"/>
+      <c r="M7" s="81"/>
+      <c r="N7" s="79"/>
+      <c r="O7" s="91"/>
+      <c r="P7" s="77"/>
+      <c r="Q7" s="77"/>
+      <c r="R7" s="77"/>
+      <c r="S7" s="77"/>
+      <c r="T7" s="77"/>
+      <c r="U7" s="77"/>
+      <c r="V7" s="77"/>
+      <c r="W7" s="77"/>
+      <c r="X7" s="88"/>
       <c r="Y7" s="2"/>
     </row>
     <row r="8" spans="1:26" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7"/>
-      <c r="B8" s="98" t="s">
+      <c r="B8" s="111" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="86" t="s">
+      <c r="C8" s="99" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="87"/>
+      <c r="D8" s="100"/>
       <c r="E8" s="35"/>
       <c r="F8" s="36"/>
       <c r="G8" s="36"/>
@@ -2229,11 +2229,11 @@
     </row>
     <row r="9" spans="1:26" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="7"/>
-      <c r="B9" s="99"/>
-      <c r="C9" s="88" t="s">
+      <c r="B9" s="112"/>
+      <c r="C9" s="101" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="89"/>
+      <c r="D9" s="102"/>
       <c r="E9" s="41"/>
       <c r="F9" s="42"/>
       <c r="G9" s="42"/>
@@ -2259,11 +2259,11 @@
     </row>
     <row r="10" spans="1:26" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7"/>
-      <c r="B10" s="99"/>
-      <c r="C10" s="90" t="s">
+      <c r="B10" s="112"/>
+      <c r="C10" s="103" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="91"/>
+      <c r="D10" s="104"/>
       <c r="E10" s="41"/>
       <c r="F10" s="42"/>
       <c r="G10" s="42"/>
@@ -2289,11 +2289,11 @@
     </row>
     <row r="11" spans="1:26" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="7"/>
-      <c r="B11" s="100"/>
-      <c r="C11" s="92" t="s">
+      <c r="B11" s="113"/>
+      <c r="C11" s="105" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="93"/>
+      <c r="D11" s="106"/>
       <c r="E11" s="46"/>
       <c r="F11" s="47"/>
       <c r="G11" s="47"/>
@@ -2319,13 +2319,13 @@
     </row>
     <row r="12" spans="1:26" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="7"/>
-      <c r="B12" s="79" t="s">
+      <c r="B12" s="92" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="94" t="s">
+      <c r="C12" s="107" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="95"/>
+      <c r="D12" s="108"/>
       <c r="E12" s="17"/>
       <c r="F12" s="18"/>
       <c r="G12" s="18"/>
@@ -2351,20 +2351,22 @@
     </row>
     <row r="13" spans="1:26" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="7"/>
-      <c r="B13" s="80"/>
-      <c r="C13" s="96" t="s">
+      <c r="B13" s="93"/>
+      <c r="C13" s="109" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="97"/>
+      <c r="D13" s="110"/>
       <c r="E13" s="21"/>
-      <c r="F13" s="122" t="s">
+      <c r="F13" s="72" t="s">
         <v>72</v>
       </c>
       <c r="G13" s="23"/>
       <c r="H13" s="24"/>
       <c r="I13" s="24"/>
       <c r="J13" s="22"/>
-      <c r="K13" s="22"/>
+      <c r="K13" s="72" t="s">
+        <v>72</v>
+      </c>
       <c r="L13" s="23"/>
       <c r="M13" s="24"/>
       <c r="N13" s="25"/>
@@ -2383,26 +2385,30 @@
     </row>
     <row r="14" spans="1:26" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="7"/>
-      <c r="B14" s="80"/>
-      <c r="C14" s="82" t="s">
+      <c r="B14" s="93"/>
+      <c r="C14" s="95" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="83"/>
-      <c r="E14" s="122" t="s">
+      <c r="D14" s="96"/>
+      <c r="E14" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="F14" s="122" t="s">
+      <c r="F14" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="G14" s="122" t="s">
+      <c r="G14" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="H14" s="122" t="s">
+      <c r="H14" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="I14" s="22"/>
+      <c r="I14" s="72" t="s">
+        <v>72</v>
+      </c>
       <c r="J14" s="24"/>
-      <c r="K14" s="22"/>
+      <c r="K14" s="72" t="s">
+        <v>72</v>
+      </c>
       <c r="L14" s="22"/>
       <c r="M14" s="24"/>
       <c r="N14" s="25"/>
@@ -2421,15 +2427,15 @@
     </row>
     <row r="15" spans="1:26" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="7"/>
-      <c r="B15" s="80"/>
-      <c r="C15" s="82" t="s">
+      <c r="B15" s="93"/>
+      <c r="C15" s="95" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="83"/>
+      <c r="D15" s="96"/>
       <c r="E15" s="21"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="122" t="s">
+      <c r="H15" s="72" t="s">
         <v>72</v>
       </c>
       <c r="I15" s="23"/>
@@ -2453,15 +2459,15 @@
     </row>
     <row r="16" spans="1:26" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="7"/>
-      <c r="B16" s="80"/>
-      <c r="C16" s="82" t="s">
+      <c r="B16" s="93"/>
+      <c r="C16" s="95" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="83"/>
+      <c r="D16" s="96"/>
       <c r="E16" s="27"/>
       <c r="F16" s="28"/>
       <c r="G16" s="23"/>
-      <c r="H16" s="122" t="s">
+      <c r="H16" s="72" t="s">
         <v>72</v>
       </c>
       <c r="I16" s="24"/>
@@ -2485,11 +2491,11 @@
     </row>
     <row r="17" spans="1:27" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="7"/>
-      <c r="B17" s="81"/>
-      <c r="C17" s="84" t="s">
+      <c r="B17" s="94"/>
+      <c r="C17" s="97" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="85"/>
+      <c r="D17" s="98"/>
       <c r="E17" s="29"/>
       <c r="F17" s="30"/>
       <c r="G17" s="31"/>
@@ -2543,16 +2549,16 @@
     </row>
     <row r="19" spans="1:27" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B19" s="22"/>
-      <c r="C19" s="110" t="s">
+      <c r="C19" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="D19" s="111"/>
-      <c r="E19" s="111"/>
-      <c r="F19" s="111"/>
-      <c r="G19" s="111"/>
-      <c r="H19" s="111"/>
-      <c r="I19" s="111"/>
-      <c r="J19" s="111"/>
+      <c r="D19" s="74"/>
+      <c r="E19" s="74"/>
+      <c r="F19" s="74"/>
+      <c r="G19" s="74"/>
+      <c r="H19" s="74"/>
+      <c r="I19" s="74"/>
+      <c r="J19" s="74"/>
       <c r="L19" s="62"/>
       <c r="M19" s="61"/>
       <c r="N19" s="64" t="s">
@@ -2582,23 +2588,23 @@
     </row>
     <row r="21" spans="1:27" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="24"/>
-      <c r="C21" s="110" t="s">
+      <c r="C21" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="D21" s="111"/>
-      <c r="E21" s="111"/>
-      <c r="F21" s="111"/>
-      <c r="G21" s="111"/>
-      <c r="H21" s="111"/>
-      <c r="I21" s="111"/>
-      <c r="J21" s="111"/>
-      <c r="M21" s="118" t="s">
+      <c r="D21" s="74"/>
+      <c r="E21" s="74"/>
+      <c r="F21" s="74"/>
+      <c r="G21" s="74"/>
+      <c r="H21" s="74"/>
+      <c r="I21" s="74"/>
+      <c r="J21" s="74"/>
+      <c r="M21" s="84" t="s">
         <v>63</v>
       </c>
-      <c r="N21" s="72" t="s">
+      <c r="N21" s="114" t="s">
         <v>63</v>
       </c>
-      <c r="O21" s="74" t="s">
+      <c r="O21" s="116" t="s">
         <v>63</v>
       </c>
       <c r="Q21"/>
@@ -2613,9 +2619,9 @@
       <c r="H22" s="55"/>
       <c r="I22" s="55"/>
       <c r="J22" s="55"/>
-      <c r="M22" s="119"/>
-      <c r="N22" s="73"/>
-      <c r="O22" s="75"/>
+      <c r="M22" s="85"/>
+      <c r="N22" s="115"/>
+      <c r="O22" s="117"/>
       <c r="Q22" s="56" t="s">
         <v>55</v>
       </c>
@@ -2623,24 +2629,24 @@
     </row>
     <row r="23" spans="1:27" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="23"/>
-      <c r="C23" s="110" t="s">
+      <c r="C23" s="73" t="s">
         <v>38</v>
       </c>
-      <c r="D23" s="111"/>
-      <c r="E23" s="111"/>
-      <c r="F23" s="111"/>
-      <c r="G23" s="111"/>
-      <c r="H23" s="111"/>
-      <c r="I23" s="111"/>
-      <c r="J23" s="111"/>
+      <c r="D23" s="74"/>
+      <c r="E23" s="74"/>
+      <c r="F23" s="74"/>
+      <c r="G23" s="74"/>
+      <c r="H23" s="74"/>
+      <c r="I23" s="74"/>
+      <c r="J23" s="74"/>
       <c r="K23" s="56"/>
-      <c r="M23" s="76" t="s">
+      <c r="M23" s="118" t="s">
         <v>35</v>
       </c>
-      <c r="N23" s="78" t="s">
+      <c r="N23" s="120" t="s">
         <v>36</v>
       </c>
-      <c r="O23" s="76" t="s">
+      <c r="O23" s="118" t="s">
         <v>37</v>
       </c>
       <c r="AA23" s="10"/>
@@ -2648,9 +2654,9 @@
     <row r="24" spans="1:27" x14ac:dyDescent="0.35">
       <c r="K24" s="56"/>
       <c r="L24"/>
-      <c r="M24" s="77"/>
-      <c r="N24" s="77"/>
-      <c r="O24" s="77"/>
+      <c r="M24" s="119"/>
+      <c r="N24" s="119"/>
+      <c r="O24" s="119"/>
       <c r="P24"/>
       <c r="AA24" s="10"/>
     </row>
@@ -2663,6 +2669,31 @@
     </row>
   </sheetData>
   <mergeCells count="41">
+    <mergeCell ref="N21:N22"/>
+    <mergeCell ref="O21:O22"/>
+    <mergeCell ref="M23:M24"/>
+    <mergeCell ref="N23:N24"/>
+    <mergeCell ref="O23:O24"/>
+    <mergeCell ref="B12:B17"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="X4:X7"/>
+    <mergeCell ref="O4:O7"/>
+    <mergeCell ref="S4:S7"/>
+    <mergeCell ref="P4:P7"/>
+    <mergeCell ref="Q4:Q7"/>
+    <mergeCell ref="R4:R7"/>
+    <mergeCell ref="T4:T7"/>
+    <mergeCell ref="V4:V7"/>
     <mergeCell ref="C21:J21"/>
     <mergeCell ref="C23:J23"/>
     <mergeCell ref="U4:U7"/>
@@ -2679,31 +2710,6 @@
     <mergeCell ref="H4:H7"/>
     <mergeCell ref="I4:I7"/>
     <mergeCell ref="M21:M22"/>
-    <mergeCell ref="X4:X7"/>
-    <mergeCell ref="O4:O7"/>
-    <mergeCell ref="S4:S7"/>
-    <mergeCell ref="P4:P7"/>
-    <mergeCell ref="Q4:Q7"/>
-    <mergeCell ref="R4:R7"/>
-    <mergeCell ref="T4:T7"/>
-    <mergeCell ref="V4:V7"/>
-    <mergeCell ref="B12:B17"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="N21:N22"/>
-    <mergeCell ref="O21:O22"/>
-    <mergeCell ref="M23:M24"/>
-    <mergeCell ref="N23:N24"/>
-    <mergeCell ref="O23:O24"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2721,351 +2727,351 @@
   <sheetData>
     <row r="1" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B2" s="120" t="s">
+      <c r="B2" s="121" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="120"/>
-      <c r="D2" s="120"/>
-      <c r="E2" s="120"/>
-      <c r="F2" s="120"/>
-      <c r="G2" s="120"/>
-      <c r="H2" s="120"/>
-      <c r="I2" s="120"/>
-      <c r="J2" s="120"/>
-      <c r="K2" s="120"/>
-      <c r="L2" s="120"/>
-      <c r="M2" s="120"/>
-      <c r="N2" s="120"/>
+      <c r="C2" s="121"/>
+      <c r="D2" s="121"/>
+      <c r="E2" s="121"/>
+      <c r="F2" s="121"/>
+      <c r="G2" s="121"/>
+      <c r="H2" s="121"/>
+      <c r="I2" s="121"/>
+      <c r="J2" s="121"/>
+      <c r="K2" s="121"/>
+      <c r="L2" s="121"/>
+      <c r="M2" s="121"/>
+      <c r="N2" s="121"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B3" s="121"/>
-      <c r="C3" s="121"/>
-      <c r="D3" s="121"/>
-      <c r="E3" s="121"/>
-      <c r="F3" s="121"/>
-      <c r="G3" s="121"/>
-      <c r="H3" s="121"/>
-      <c r="I3" s="121"/>
-      <c r="J3" s="121"/>
-      <c r="K3" s="121"/>
-      <c r="L3" s="121"/>
-      <c r="M3" s="121"/>
-      <c r="N3" s="121"/>
+      <c r="B3" s="122"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="122"/>
+      <c r="E3" s="122"/>
+      <c r="F3" s="122"/>
+      <c r="G3" s="122"/>
+      <c r="H3" s="122"/>
+      <c r="I3" s="122"/>
+      <c r="J3" s="122"/>
+      <c r="K3" s="122"/>
+      <c r="L3" s="122"/>
+      <c r="M3" s="122"/>
+      <c r="N3" s="122"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B4" s="121"/>
-      <c r="C4" s="121"/>
-      <c r="D4" s="121"/>
-      <c r="E4" s="121"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121"/>
-      <c r="I4" s="121"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="121"/>
-      <c r="L4" s="121"/>
-      <c r="M4" s="121"/>
-      <c r="N4" s="121"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="122"/>
+      <c r="G4" s="122"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="122"/>
+      <c r="L4" s="122"/>
+      <c r="M4" s="122"/>
+      <c r="N4" s="122"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B5" s="121"/>
-      <c r="C5" s="121"/>
-      <c r="D5" s="121"/>
-      <c r="E5" s="121"/>
-      <c r="F5" s="121"/>
-      <c r="G5" s="121"/>
-      <c r="H5" s="121"/>
-      <c r="I5" s="121"/>
-      <c r="J5" s="121"/>
-      <c r="K5" s="121"/>
-      <c r="L5" s="121"/>
-      <c r="M5" s="121"/>
-      <c r="N5" s="121"/>
+      <c r="B5" s="122"/>
+      <c r="C5" s="122"/>
+      <c r="D5" s="122"/>
+      <c r="E5" s="122"/>
+      <c r="F5" s="122"/>
+      <c r="G5" s="122"/>
+      <c r="H5" s="122"/>
+      <c r="I5" s="122"/>
+      <c r="J5" s="122"/>
+      <c r="K5" s="122"/>
+      <c r="L5" s="122"/>
+      <c r="M5" s="122"/>
+      <c r="N5" s="122"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B6" s="121"/>
-      <c r="C6" s="121"/>
-      <c r="D6" s="121"/>
-      <c r="E6" s="121"/>
-      <c r="F6" s="121"/>
-      <c r="G6" s="121"/>
-      <c r="H6" s="121"/>
-      <c r="I6" s="121"/>
-      <c r="J6" s="121"/>
-      <c r="K6" s="121"/>
-      <c r="L6" s="121"/>
-      <c r="M6" s="121"/>
-      <c r="N6" s="121"/>
+      <c r="B6" s="122"/>
+      <c r="C6" s="122"/>
+      <c r="D6" s="122"/>
+      <c r="E6" s="122"/>
+      <c r="F6" s="122"/>
+      <c r="G6" s="122"/>
+      <c r="H6" s="122"/>
+      <c r="I6" s="122"/>
+      <c r="J6" s="122"/>
+      <c r="K6" s="122"/>
+      <c r="L6" s="122"/>
+      <c r="M6" s="122"/>
+      <c r="N6" s="122"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B7" s="121"/>
-      <c r="C7" s="121"/>
-      <c r="D7" s="121"/>
-      <c r="E7" s="121"/>
-      <c r="F7" s="121"/>
-      <c r="G7" s="121"/>
-      <c r="H7" s="121"/>
-      <c r="I7" s="121"/>
-      <c r="J7" s="121"/>
-      <c r="K7" s="121"/>
-      <c r="L7" s="121"/>
-      <c r="M7" s="121"/>
-      <c r="N7" s="121"/>
+      <c r="B7" s="122"/>
+      <c r="C7" s="122"/>
+      <c r="D7" s="122"/>
+      <c r="E7" s="122"/>
+      <c r="F7" s="122"/>
+      <c r="G7" s="122"/>
+      <c r="H7" s="122"/>
+      <c r="I7" s="122"/>
+      <c r="J7" s="122"/>
+      <c r="K7" s="122"/>
+      <c r="L7" s="122"/>
+      <c r="M7" s="122"/>
+      <c r="N7" s="122"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B8" s="121"/>
-      <c r="C8" s="121"/>
-      <c r="D8" s="121"/>
-      <c r="E8" s="121"/>
-      <c r="F8" s="121"/>
-      <c r="G8" s="121"/>
-      <c r="H8" s="121"/>
-      <c r="I8" s="121"/>
-      <c r="J8" s="121"/>
-      <c r="K8" s="121"/>
-      <c r="L8" s="121"/>
-      <c r="M8" s="121"/>
-      <c r="N8" s="121"/>
+      <c r="B8" s="122"/>
+      <c r="C8" s="122"/>
+      <c r="D8" s="122"/>
+      <c r="E8" s="122"/>
+      <c r="F8" s="122"/>
+      <c r="G8" s="122"/>
+      <c r="H8" s="122"/>
+      <c r="I8" s="122"/>
+      <c r="J8" s="122"/>
+      <c r="K8" s="122"/>
+      <c r="L8" s="122"/>
+      <c r="M8" s="122"/>
+      <c r="N8" s="122"/>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B9" s="121"/>
-      <c r="C9" s="121"/>
-      <c r="D9" s="121"/>
-      <c r="E9" s="121"/>
-      <c r="F9" s="121"/>
-      <c r="G9" s="121"/>
-      <c r="H9" s="121"/>
-      <c r="I9" s="121"/>
-      <c r="J9" s="121"/>
-      <c r="K9" s="121"/>
-      <c r="L9" s="121"/>
-      <c r="M9" s="121"/>
-      <c r="N9" s="121"/>
+      <c r="B9" s="122"/>
+      <c r="C9" s="122"/>
+      <c r="D9" s="122"/>
+      <c r="E9" s="122"/>
+      <c r="F9" s="122"/>
+      <c r="G9" s="122"/>
+      <c r="H9" s="122"/>
+      <c r="I9" s="122"/>
+      <c r="J9" s="122"/>
+      <c r="K9" s="122"/>
+      <c r="L9" s="122"/>
+      <c r="M9" s="122"/>
+      <c r="N9" s="122"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B10" s="121"/>
-      <c r="C10" s="121"/>
-      <c r="D10" s="121"/>
-      <c r="E10" s="121"/>
-      <c r="F10" s="121"/>
-      <c r="G10" s="121"/>
-      <c r="H10" s="121"/>
-      <c r="I10" s="121"/>
-      <c r="J10" s="121"/>
-      <c r="K10" s="121"/>
-      <c r="L10" s="121"/>
-      <c r="M10" s="121"/>
-      <c r="N10" s="121"/>
+      <c r="B10" s="122"/>
+      <c r="C10" s="122"/>
+      <c r="D10" s="122"/>
+      <c r="E10" s="122"/>
+      <c r="F10" s="122"/>
+      <c r="G10" s="122"/>
+      <c r="H10" s="122"/>
+      <c r="I10" s="122"/>
+      <c r="J10" s="122"/>
+      <c r="K10" s="122"/>
+      <c r="L10" s="122"/>
+      <c r="M10" s="122"/>
+      <c r="N10" s="122"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B11" s="121"/>
-      <c r="C11" s="121"/>
-      <c r="D11" s="121"/>
-      <c r="E11" s="121"/>
-      <c r="F11" s="121"/>
-      <c r="G11" s="121"/>
-      <c r="H11" s="121"/>
-      <c r="I11" s="121"/>
-      <c r="J11" s="121"/>
-      <c r="K11" s="121"/>
-      <c r="L11" s="121"/>
-      <c r="M11" s="121"/>
-      <c r="N11" s="121"/>
+      <c r="B11" s="122"/>
+      <c r="C11" s="122"/>
+      <c r="D11" s="122"/>
+      <c r="E11" s="122"/>
+      <c r="F11" s="122"/>
+      <c r="G11" s="122"/>
+      <c r="H11" s="122"/>
+      <c r="I11" s="122"/>
+      <c r="J11" s="122"/>
+      <c r="K11" s="122"/>
+      <c r="L11" s="122"/>
+      <c r="M11" s="122"/>
+      <c r="N11" s="122"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B12" s="121"/>
-      <c r="C12" s="121"/>
-      <c r="D12" s="121"/>
-      <c r="E12" s="121"/>
-      <c r="F12" s="121"/>
-      <c r="G12" s="121"/>
-      <c r="H12" s="121"/>
-      <c r="I12" s="121"/>
-      <c r="J12" s="121"/>
-      <c r="K12" s="121"/>
-      <c r="L12" s="121"/>
-      <c r="M12" s="121"/>
-      <c r="N12" s="121"/>
+      <c r="B12" s="122"/>
+      <c r="C12" s="122"/>
+      <c r="D12" s="122"/>
+      <c r="E12" s="122"/>
+      <c r="F12" s="122"/>
+      <c r="G12" s="122"/>
+      <c r="H12" s="122"/>
+      <c r="I12" s="122"/>
+      <c r="J12" s="122"/>
+      <c r="K12" s="122"/>
+      <c r="L12" s="122"/>
+      <c r="M12" s="122"/>
+      <c r="N12" s="122"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B13" s="121"/>
-      <c r="C13" s="121"/>
-      <c r="D13" s="121"/>
-      <c r="E13" s="121"/>
-      <c r="F13" s="121"/>
-      <c r="G13" s="121"/>
-      <c r="H13" s="121"/>
-      <c r="I13" s="121"/>
-      <c r="J13" s="121"/>
-      <c r="K13" s="121"/>
-      <c r="L13" s="121"/>
-      <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
+      <c r="B13" s="122"/>
+      <c r="C13" s="122"/>
+      <c r="D13" s="122"/>
+      <c r="E13" s="122"/>
+      <c r="F13" s="122"/>
+      <c r="G13" s="122"/>
+      <c r="H13" s="122"/>
+      <c r="I13" s="122"/>
+      <c r="J13" s="122"/>
+      <c r="K13" s="122"/>
+      <c r="L13" s="122"/>
+      <c r="M13" s="122"/>
+      <c r="N13" s="122"/>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B14" s="121"/>
-      <c r="C14" s="121"/>
-      <c r="D14" s="121"/>
-      <c r="E14" s="121"/>
-      <c r="F14" s="121"/>
-      <c r="G14" s="121"/>
-      <c r="H14" s="121"/>
-      <c r="I14" s="121"/>
-      <c r="J14" s="121"/>
-      <c r="K14" s="121"/>
-      <c r="L14" s="121"/>
-      <c r="M14" s="121"/>
-      <c r="N14" s="121"/>
+      <c r="B14" s="122"/>
+      <c r="C14" s="122"/>
+      <c r="D14" s="122"/>
+      <c r="E14" s="122"/>
+      <c r="F14" s="122"/>
+      <c r="G14" s="122"/>
+      <c r="H14" s="122"/>
+      <c r="I14" s="122"/>
+      <c r="J14" s="122"/>
+      <c r="K14" s="122"/>
+      <c r="L14" s="122"/>
+      <c r="M14" s="122"/>
+      <c r="N14" s="122"/>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B15" s="121"/>
-      <c r="C15" s="121"/>
-      <c r="D15" s="121"/>
-      <c r="E15" s="121"/>
-      <c r="F15" s="121"/>
-      <c r="G15" s="121"/>
-      <c r="H15" s="121"/>
-      <c r="I15" s="121"/>
-      <c r="J15" s="121"/>
-      <c r="K15" s="121"/>
-      <c r="L15" s="121"/>
-      <c r="M15" s="121"/>
-      <c r="N15" s="121"/>
+      <c r="B15" s="122"/>
+      <c r="C15" s="122"/>
+      <c r="D15" s="122"/>
+      <c r="E15" s="122"/>
+      <c r="F15" s="122"/>
+      <c r="G15" s="122"/>
+      <c r="H15" s="122"/>
+      <c r="I15" s="122"/>
+      <c r="J15" s="122"/>
+      <c r="K15" s="122"/>
+      <c r="L15" s="122"/>
+      <c r="M15" s="122"/>
+      <c r="N15" s="122"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B16" s="121"/>
-      <c r="C16" s="121"/>
-      <c r="D16" s="121"/>
-      <c r="E16" s="121"/>
-      <c r="F16" s="121"/>
-      <c r="G16" s="121"/>
-      <c r="H16" s="121"/>
-      <c r="I16" s="121"/>
-      <c r="J16" s="121"/>
-      <c r="K16" s="121"/>
-      <c r="L16" s="121"/>
-      <c r="M16" s="121"/>
-      <c r="N16" s="121"/>
+      <c r="B16" s="122"/>
+      <c r="C16" s="122"/>
+      <c r="D16" s="122"/>
+      <c r="E16" s="122"/>
+      <c r="F16" s="122"/>
+      <c r="G16" s="122"/>
+      <c r="H16" s="122"/>
+      <c r="I16" s="122"/>
+      <c r="J16" s="122"/>
+      <c r="K16" s="122"/>
+      <c r="L16" s="122"/>
+      <c r="M16" s="122"/>
+      <c r="N16" s="122"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B17" s="121"/>
-      <c r="C17" s="121"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="121"/>
-      <c r="G17" s="121"/>
-      <c r="H17" s="121"/>
-      <c r="I17" s="121"/>
-      <c r="J17" s="121"/>
-      <c r="K17" s="121"/>
-      <c r="L17" s="121"/>
-      <c r="M17" s="121"/>
-      <c r="N17" s="121"/>
+      <c r="B17" s="122"/>
+      <c r="C17" s="122"/>
+      <c r="D17" s="122"/>
+      <c r="E17" s="122"/>
+      <c r="F17" s="122"/>
+      <c r="G17" s="122"/>
+      <c r="H17" s="122"/>
+      <c r="I17" s="122"/>
+      <c r="J17" s="122"/>
+      <c r="K17" s="122"/>
+      <c r="L17" s="122"/>
+      <c r="M17" s="122"/>
+      <c r="N17" s="122"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B18" s="121"/>
-      <c r="C18" s="121"/>
-      <c r="D18" s="121"/>
-      <c r="E18" s="121"/>
-      <c r="F18" s="121"/>
-      <c r="G18" s="121"/>
-      <c r="H18" s="121"/>
-      <c r="I18" s="121"/>
-      <c r="J18" s="121"/>
-      <c r="K18" s="121"/>
-      <c r="L18" s="121"/>
-      <c r="M18" s="121"/>
-      <c r="N18" s="121"/>
+      <c r="B18" s="122"/>
+      <c r="C18" s="122"/>
+      <c r="D18" s="122"/>
+      <c r="E18" s="122"/>
+      <c r="F18" s="122"/>
+      <c r="G18" s="122"/>
+      <c r="H18" s="122"/>
+      <c r="I18" s="122"/>
+      <c r="J18" s="122"/>
+      <c r="K18" s="122"/>
+      <c r="L18" s="122"/>
+      <c r="M18" s="122"/>
+      <c r="N18" s="122"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B19" s="121"/>
-      <c r="C19" s="121"/>
-      <c r="D19" s="121"/>
-      <c r="E19" s="121"/>
-      <c r="F19" s="121"/>
-      <c r="G19" s="121"/>
-      <c r="H19" s="121"/>
-      <c r="I19" s="121"/>
-      <c r="J19" s="121"/>
-      <c r="K19" s="121"/>
-      <c r="L19" s="121"/>
-      <c r="M19" s="121"/>
-      <c r="N19" s="121"/>
+      <c r="B19" s="122"/>
+      <c r="C19" s="122"/>
+      <c r="D19" s="122"/>
+      <c r="E19" s="122"/>
+      <c r="F19" s="122"/>
+      <c r="G19" s="122"/>
+      <c r="H19" s="122"/>
+      <c r="I19" s="122"/>
+      <c r="J19" s="122"/>
+      <c r="K19" s="122"/>
+      <c r="L19" s="122"/>
+      <c r="M19" s="122"/>
+      <c r="N19" s="122"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B20" s="121"/>
-      <c r="C20" s="121"/>
-      <c r="D20" s="121"/>
-      <c r="E20" s="121"/>
-      <c r="F20" s="121"/>
-      <c r="G20" s="121"/>
-      <c r="H20" s="121"/>
-      <c r="I20" s="121"/>
-      <c r="J20" s="121"/>
-      <c r="K20" s="121"/>
-      <c r="L20" s="121"/>
-      <c r="M20" s="121"/>
-      <c r="N20" s="121"/>
+      <c r="B20" s="122"/>
+      <c r="C20" s="122"/>
+      <c r="D20" s="122"/>
+      <c r="E20" s="122"/>
+      <c r="F20" s="122"/>
+      <c r="G20" s="122"/>
+      <c r="H20" s="122"/>
+      <c r="I20" s="122"/>
+      <c r="J20" s="122"/>
+      <c r="K20" s="122"/>
+      <c r="L20" s="122"/>
+      <c r="M20" s="122"/>
+      <c r="N20" s="122"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B21" s="121"/>
-      <c r="C21" s="121"/>
-      <c r="D21" s="121"/>
-      <c r="E21" s="121"/>
-      <c r="F21" s="121"/>
-      <c r="G21" s="121"/>
-      <c r="H21" s="121"/>
-      <c r="I21" s="121"/>
-      <c r="J21" s="121"/>
-      <c r="K21" s="121"/>
-      <c r="L21" s="121"/>
-      <c r="M21" s="121"/>
-      <c r="N21" s="121"/>
+      <c r="B21" s="122"/>
+      <c r="C21" s="122"/>
+      <c r="D21" s="122"/>
+      <c r="E21" s="122"/>
+      <c r="F21" s="122"/>
+      <c r="G21" s="122"/>
+      <c r="H21" s="122"/>
+      <c r="I21" s="122"/>
+      <c r="J21" s="122"/>
+      <c r="K21" s="122"/>
+      <c r="L21" s="122"/>
+      <c r="M21" s="122"/>
+      <c r="N21" s="122"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B22" s="121"/>
-      <c r="C22" s="121"/>
-      <c r="D22" s="121"/>
-      <c r="E22" s="121"/>
-      <c r="F22" s="121"/>
-      <c r="G22" s="121"/>
-      <c r="H22" s="121"/>
-      <c r="I22" s="121"/>
-      <c r="J22" s="121"/>
-      <c r="K22" s="121"/>
-      <c r="L22" s="121"/>
-      <c r="M22" s="121"/>
-      <c r="N22" s="121"/>
+      <c r="B22" s="122"/>
+      <c r="C22" s="122"/>
+      <c r="D22" s="122"/>
+      <c r="E22" s="122"/>
+      <c r="F22" s="122"/>
+      <c r="G22" s="122"/>
+      <c r="H22" s="122"/>
+      <c r="I22" s="122"/>
+      <c r="J22" s="122"/>
+      <c r="K22" s="122"/>
+      <c r="L22" s="122"/>
+      <c r="M22" s="122"/>
+      <c r="N22" s="122"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B23" s="121"/>
-      <c r="C23" s="121"/>
-      <c r="D23" s="121"/>
-      <c r="E23" s="121"/>
-      <c r="F23" s="121"/>
-      <c r="G23" s="121"/>
-      <c r="H23" s="121"/>
-      <c r="I23" s="121"/>
-      <c r="J23" s="121"/>
-      <c r="K23" s="121"/>
-      <c r="L23" s="121"/>
-      <c r="M23" s="121"/>
-      <c r="N23" s="121"/>
+      <c r="B23" s="122"/>
+      <c r="C23" s="122"/>
+      <c r="D23" s="122"/>
+      <c r="E23" s="122"/>
+      <c r="F23" s="122"/>
+      <c r="G23" s="122"/>
+      <c r="H23" s="122"/>
+      <c r="I23" s="122"/>
+      <c r="J23" s="122"/>
+      <c r="K23" s="122"/>
+      <c r="L23" s="122"/>
+      <c r="M23" s="122"/>
+      <c r="N23" s="122"/>
     </row>
     <row r="24" spans="2:14" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="121"/>
-      <c r="C24" s="121"/>
-      <c r="D24" s="121"/>
-      <c r="E24" s="121"/>
-      <c r="F24" s="121"/>
-      <c r="G24" s="121"/>
-      <c r="H24" s="121"/>
-      <c r="I24" s="121"/>
-      <c r="J24" s="121"/>
-      <c r="K24" s="121"/>
-      <c r="L24" s="121"/>
-      <c r="M24" s="121"/>
-      <c r="N24" s="121"/>
+      <c r="B24" s="122"/>
+      <c r="C24" s="122"/>
+      <c r="D24" s="122"/>
+      <c r="E24" s="122"/>
+      <c r="F24" s="122"/>
+      <c r="G24" s="122"/>
+      <c r="H24" s="122"/>
+      <c r="I24" s="122"/>
+      <c r="J24" s="122"/>
+      <c r="K24" s="122"/>
+      <c r="L24" s="122"/>
+      <c r="M24" s="122"/>
+      <c r="N24" s="122"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3347,6 +3353,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="cc018f0f-33de-4c4c-920d-26dc6e1acc33" xsi:nil="true"/>
@@ -3357,15 +3372,6 @@
     <Description xmlns="8e39aab0-005d-45b6-a80e-05e5df2908d1" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3388,6 +3394,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FEB2382-117C-4B02-B61B-7207F73C69D2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA41F33-D73A-4946-89E5-437EF57CC713}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -3402,12 +3416,4 @@
     <ds:schemaRef ds:uri="8e39aab0-005d-45b6-a80e-05e5df2908d1"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FEB2382-117C-4B02-B61B-7207F73C69D2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/doc/AI-S4_portfoliomatrix.xlsx
+++ b/doc/AI-S4_portfoliomatrix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mathi\Documents\hu\S4\ai-s4_student\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E76CA1-AF12-49B2-9A5E-6872BB60F71D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E40EF0D9-C7C3-46C3-9D82-8289C68748FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{9145D055-8147-4D48-BED2-085A2CF38ACC}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{9145D055-8147-4D48-BED2-085A2CF38ACC}"/>
   </bookViews>
   <sheets>
     <sheet name="AI-S4" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="72">
   <si>
     <t>Leeruitkomsten</t>
   </si>
@@ -393,9 +393,6 @@
   </si>
   <si>
     <t>Mathijs de Jong</t>
-  </si>
-  <si>
-    <t>23/03/2026</t>
   </si>
   <si>
     <t>X</t>
@@ -1369,9 +1366,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -1408,15 +1402,15 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -1566,6 +1560,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2034,71 +2031,71 @@
     </row>
     <row r="4" spans="1:26" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7"/>
-      <c r="B4" s="58" t="s">
+      <c r="B4" s="57" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>70</v>
       </c>
       <c r="D4" s="13"/>
-      <c r="E4" s="82" t="s">
+      <c r="E4" s="81" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="80" t="s">
+      <c r="F4" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="80" t="s">
+      <c r="G4" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="H4" s="80" t="s">
+      <c r="H4" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="I4" s="80" t="s">
+      <c r="I4" s="79" t="s">
         <v>68</v>
       </c>
-      <c r="J4" s="80" t="s">
+      <c r="J4" s="79" t="s">
         <v>66</v>
       </c>
-      <c r="K4" s="80" t="s">
+      <c r="K4" s="79" t="s">
         <v>69</v>
       </c>
-      <c r="L4" s="80" t="s">
+      <c r="L4" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="M4" s="80" t="s">
+      <c r="M4" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="N4" s="78" t="s">
+      <c r="N4" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="O4" s="89" t="s">
+      <c r="O4" s="88" t="s">
         <v>28</v>
       </c>
-      <c r="P4" s="75" t="s">
+      <c r="P4" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="Q4" s="75" t="s">
+      <c r="Q4" s="74" t="s">
         <v>30</v>
       </c>
-      <c r="R4" s="75" t="s">
+      <c r="R4" s="74" t="s">
         <v>15</v>
       </c>
-      <c r="S4" s="75" t="s">
+      <c r="S4" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="T4" s="75" t="s">
+      <c r="T4" s="74" t="s">
         <v>17</v>
       </c>
-      <c r="U4" s="75" t="s">
+      <c r="U4" s="74" t="s">
         <v>58</v>
       </c>
-      <c r="V4" s="75" t="s">
+      <c r="V4" s="74" t="s">
         <v>56</v>
       </c>
-      <c r="W4" s="75" t="s">
+      <c r="W4" s="74" t="s">
         <v>32</v>
       </c>
-      <c r="X4" s="86" t="s">
+      <c r="X4" s="85" t="s">
         <v>31</v>
       </c>
       <c r="Y4" s="9"/>
@@ -2106,65 +2103,65 @@
     </row>
     <row r="5" spans="1:26" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7"/>
-      <c r="B5" s="59" t="s">
+      <c r="B5" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="57" t="s">
-        <v>71</v>
+      <c r="C5" s="122">
+        <v>46147</v>
       </c>
       <c r="D5" s="16"/>
-      <c r="E5" s="83"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="81"/>
-      <c r="H5" s="81"/>
-      <c r="I5" s="81"/>
-      <c r="J5" s="81"/>
-      <c r="K5" s="81"/>
-      <c r="L5" s="81"/>
-      <c r="M5" s="81"/>
-      <c r="N5" s="79"/>
-      <c r="O5" s="90"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="76"/>
-      <c r="U5" s="76"/>
-      <c r="V5" s="76"/>
-      <c r="W5" s="76"/>
-      <c r="X5" s="87"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="80"/>
+      <c r="J5" s="80"/>
+      <c r="K5" s="80"/>
+      <c r="L5" s="80"/>
+      <c r="M5" s="80"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="75"/>
+      <c r="Q5" s="75"/>
+      <c r="R5" s="75"/>
+      <c r="S5" s="75"/>
+      <c r="T5" s="75"/>
+      <c r="U5" s="75"/>
+      <c r="V5" s="75"/>
+      <c r="W5" s="75"/>
+      <c r="X5" s="86"/>
       <c r="Y5" s="9"/>
       <c r="Z5"/>
     </row>
     <row r="6" spans="1:26" ht="50.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="7"/>
-      <c r="B6" s="60" t="s">
+      <c r="B6" s="59" t="s">
         <v>42</v>
       </c>
       <c r="C6" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" s="16"/>
-      <c r="E6" s="83"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="81"/>
-      <c r="H6" s="81"/>
-      <c r="I6" s="81"/>
-      <c r="J6" s="81"/>
-      <c r="K6" s="81"/>
-      <c r="L6" s="81"/>
-      <c r="M6" s="81"/>
-      <c r="N6" s="79"/>
-      <c r="O6" s="90"/>
-      <c r="P6" s="76"/>
-      <c r="Q6" s="76"/>
-      <c r="R6" s="76"/>
-      <c r="S6" s="76"/>
-      <c r="T6" s="76"/>
-      <c r="U6" s="76"/>
-      <c r="V6" s="76"/>
-      <c r="W6" s="76"/>
-      <c r="X6" s="87"/>
+      <c r="E6" s="82"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
+      <c r="J6" s="80"/>
+      <c r="K6" s="80"/>
+      <c r="L6" s="80"/>
+      <c r="M6" s="80"/>
+      <c r="N6" s="78"/>
+      <c r="O6" s="89"/>
+      <c r="P6" s="75"/>
+      <c r="Q6" s="75"/>
+      <c r="R6" s="75"/>
+      <c r="S6" s="75"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
+      <c r="V6" s="75"/>
+      <c r="W6" s="75"/>
+      <c r="X6" s="86"/>
       <c r="Y6" s="9"/>
       <c r="Z6"/>
     </row>
@@ -2173,37 +2170,37 @@
       <c r="B7" s="2"/>
       <c r="C7" s="4"/>
       <c r="D7" s="5"/>
-      <c r="E7" s="83"/>
-      <c r="F7" s="81"/>
-      <c r="G7" s="81"/>
-      <c r="H7" s="81"/>
-      <c r="I7" s="81"/>
-      <c r="J7" s="81"/>
-      <c r="K7" s="81"/>
-      <c r="L7" s="81"/>
-      <c r="M7" s="81"/>
-      <c r="N7" s="79"/>
-      <c r="O7" s="91"/>
-      <c r="P7" s="77"/>
-      <c r="Q7" s="77"/>
-      <c r="R7" s="77"/>
-      <c r="S7" s="77"/>
-      <c r="T7" s="77"/>
-      <c r="U7" s="77"/>
-      <c r="V7" s="77"/>
-      <c r="W7" s="77"/>
-      <c r="X7" s="88"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="80"/>
+      <c r="G7" s="80"/>
+      <c r="H7" s="80"/>
+      <c r="I7" s="80"/>
+      <c r="J7" s="80"/>
+      <c r="K7" s="80"/>
+      <c r="L7" s="80"/>
+      <c r="M7" s="80"/>
+      <c r="N7" s="78"/>
+      <c r="O7" s="90"/>
+      <c r="P7" s="76"/>
+      <c r="Q7" s="76"/>
+      <c r="R7" s="76"/>
+      <c r="S7" s="76"/>
+      <c r="T7" s="76"/>
+      <c r="U7" s="76"/>
+      <c r="V7" s="76"/>
+      <c r="W7" s="76"/>
+      <c r="X7" s="87"/>
       <c r="Y7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:26" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="7"/>
-      <c r="B8" s="111" t="s">
+      <c r="B8" s="110" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="99" t="s">
+      <c r="C8" s="98" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="100"/>
+      <c r="D8" s="99"/>
       <c r="E8" s="35"/>
       <c r="F8" s="36"/>
       <c r="G8" s="36"/>
@@ -2216,7 +2213,9 @@
       <c r="N8" s="38"/>
       <c r="O8" s="37"/>
       <c r="P8" s="37"/>
-      <c r="Q8" s="39"/>
+      <c r="Q8" s="71" t="s">
+        <v>71</v>
+      </c>
       <c r="R8" s="37"/>
       <c r="S8" s="37"/>
       <c r="T8" s="37"/>
@@ -2227,13 +2226,13 @@
       <c r="Y8" s="7"/>
       <c r="Z8"/>
     </row>
-    <row r="9" spans="1:26" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:26" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="7"/>
-      <c r="B9" s="112"/>
-      <c r="C9" s="101" t="s">
+      <c r="B9" s="111"/>
+      <c r="C9" s="100" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="102"/>
+      <c r="D9" s="101"/>
       <c r="E9" s="41"/>
       <c r="F9" s="42"/>
       <c r="G9" s="42"/>
@@ -2244,9 +2243,13 @@
       <c r="L9" s="42"/>
       <c r="M9" s="42"/>
       <c r="N9" s="43"/>
-      <c r="O9" s="44"/>
-      <c r="P9" s="65"/>
-      <c r="Q9" s="44"/>
+      <c r="O9" s="71" t="s">
+        <v>71</v>
+      </c>
+      <c r="P9" s="64"/>
+      <c r="Q9" s="71" t="s">
+        <v>71</v>
+      </c>
       <c r="R9" s="44"/>
       <c r="S9" s="44"/>
       <c r="T9" s="44"/>
@@ -2257,13 +2260,13 @@
       <c r="Y9" s="7"/>
       <c r="Z9"/>
     </row>
-    <row r="10" spans="1:26" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:26" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="7"/>
-      <c r="B10" s="112"/>
-      <c r="C10" s="103" t="s">
+      <c r="B10" s="111"/>
+      <c r="C10" s="102" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="104"/>
+      <c r="D10" s="103"/>
       <c r="E10" s="41"/>
       <c r="F10" s="42"/>
       <c r="G10" s="42"/>
@@ -2274,9 +2277,13 @@
       <c r="L10" s="42"/>
       <c r="M10" s="42"/>
       <c r="N10" s="43"/>
-      <c r="O10" s="44"/>
-      <c r="P10" s="65"/>
-      <c r="Q10" s="44"/>
+      <c r="O10" s="71" t="s">
+        <v>71</v>
+      </c>
+      <c r="P10" s="64"/>
+      <c r="Q10" s="71" t="s">
+        <v>71</v>
+      </c>
       <c r="R10" s="44"/>
       <c r="S10" s="44"/>
       <c r="T10" s="44"/>
@@ -2289,11 +2296,11 @@
     </row>
     <row r="11" spans="1:26" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="7"/>
-      <c r="B11" s="113"/>
-      <c r="C11" s="105" t="s">
+      <c r="B11" s="112"/>
+      <c r="C11" s="104" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="106"/>
+      <c r="D11" s="105"/>
       <c r="E11" s="46"/>
       <c r="F11" s="47"/>
       <c r="G11" s="47"/>
@@ -2304,14 +2311,18 @@
       <c r="L11" s="47"/>
       <c r="M11" s="47"/>
       <c r="N11" s="48"/>
-      <c r="O11" s="70"/>
+      <c r="O11" s="71" t="s">
+        <v>71</v>
+      </c>
       <c r="P11" s="49"/>
-      <c r="Q11" s="71"/>
-      <c r="R11" s="71"/>
-      <c r="S11" s="71"/>
-      <c r="T11" s="71"/>
-      <c r="U11" s="71"/>
-      <c r="V11" s="71"/>
+      <c r="Q11" s="71" t="s">
+        <v>71</v>
+      </c>
+      <c r="R11" s="69"/>
+      <c r="S11" s="69"/>
+      <c r="T11" s="69"/>
+      <c r="U11" s="69"/>
+      <c r="V11" s="69"/>
       <c r="W11" s="47"/>
       <c r="X11" s="50"/>
       <c r="Y11" s="7"/>
@@ -2319,13 +2330,13 @@
     </row>
     <row r="12" spans="1:26" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="7"/>
-      <c r="B12" s="92" t="s">
+      <c r="B12" s="91" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="107" t="s">
+      <c r="C12" s="106" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="108"/>
+      <c r="D12" s="107"/>
       <c r="E12" s="17"/>
       <c r="F12" s="18"/>
       <c r="G12" s="18"/>
@@ -2336,43 +2347,47 @@
       <c r="L12" s="19"/>
       <c r="M12" s="18"/>
       <c r="N12" s="20"/>
-      <c r="O12" s="66"/>
-      <c r="P12" s="67"/>
-      <c r="Q12" s="68"/>
-      <c r="R12" s="67"/>
-      <c r="S12" s="66"/>
-      <c r="T12" s="66"/>
-      <c r="U12" s="66"/>
-      <c r="V12" s="67"/>
-      <c r="W12" s="68"/>
-      <c r="X12" s="69"/>
+      <c r="O12" s="65"/>
+      <c r="P12" s="66"/>
+      <c r="Q12" s="70" t="s">
+        <v>71</v>
+      </c>
+      <c r="R12" s="66"/>
+      <c r="S12" s="65"/>
+      <c r="T12" s="65"/>
+      <c r="U12" s="65"/>
+      <c r="V12" s="66"/>
+      <c r="W12" s="67"/>
+      <c r="X12" s="68"/>
       <c r="Y12" s="7"/>
       <c r="Z12"/>
     </row>
     <row r="13" spans="1:26" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="7"/>
-      <c r="B13" s="93"/>
-      <c r="C13" s="109" t="s">
+      <c r="B13" s="92"/>
+      <c r="C13" s="108" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="110"/>
+      <c r="D13" s="109"/>
       <c r="E13" s="21"/>
-      <c r="F13" s="72" t="s">
-        <v>72</v>
+      <c r="F13" s="70" t="s">
+        <v>71</v>
       </c>
       <c r="G13" s="23"/>
       <c r="H13" s="24"/>
       <c r="I13" s="24"/>
       <c r="J13" s="22"/>
-      <c r="K13" s="72" t="s">
-        <v>72</v>
+      <c r="K13" s="70" t="s">
+        <v>71</v>
       </c>
       <c r="L13" s="23"/>
       <c r="M13" s="24"/>
       <c r="N13" s="25"/>
       <c r="O13" s="24"/>
       <c r="P13" s="23"/>
-      <c r="Q13" s="22"/>
+      <c r="Q13" s="70" t="s">
+        <v>71</v>
+      </c>
       <c r="R13" s="24"/>
       <c r="S13" s="24"/>
       <c r="T13" s="24"/>
@@ -2385,36 +2400,38 @@
     </row>
     <row r="14" spans="1:26" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="7"/>
-      <c r="B14" s="93"/>
-      <c r="C14" s="95" t="s">
+      <c r="B14" s="92"/>
+      <c r="C14" s="94" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="96"/>
-      <c r="E14" s="72" t="s">
-        <v>72</v>
-      </c>
-      <c r="F14" s="72" t="s">
-        <v>72</v>
-      </c>
-      <c r="G14" s="72" t="s">
-        <v>72</v>
-      </c>
-      <c r="H14" s="72" t="s">
-        <v>72</v>
-      </c>
-      <c r="I14" s="72" t="s">
-        <v>72</v>
+      <c r="D14" s="95"/>
+      <c r="E14" s="70" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14" s="70" t="s">
+        <v>71</v>
+      </c>
+      <c r="G14" s="70" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" s="70" t="s">
+        <v>71</v>
+      </c>
+      <c r="I14" s="70" t="s">
+        <v>71</v>
       </c>
       <c r="J14" s="24"/>
-      <c r="K14" s="72" t="s">
-        <v>72</v>
+      <c r="K14" s="70" t="s">
+        <v>71</v>
       </c>
       <c r="L14" s="22"/>
       <c r="M14" s="24"/>
       <c r="N14" s="25"/>
       <c r="O14" s="21"/>
       <c r="P14" s="24"/>
-      <c r="Q14" s="22"/>
+      <c r="Q14" s="70" t="s">
+        <v>71</v>
+      </c>
       <c r="R14" s="24"/>
       <c r="S14" s="24"/>
       <c r="T14" s="24"/>
@@ -2427,16 +2444,16 @@
     </row>
     <row r="15" spans="1:26" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="7"/>
-      <c r="B15" s="93"/>
-      <c r="C15" s="95" t="s">
+      <c r="B15" s="92"/>
+      <c r="C15" s="94" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="96"/>
+      <c r="D15" s="95"/>
       <c r="E15" s="21"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="72" t="s">
-        <v>72</v>
+      <c r="H15" s="70" t="s">
+        <v>71</v>
       </c>
       <c r="I15" s="23"/>
       <c r="J15" s="22"/>
@@ -2446,7 +2463,9 @@
       <c r="N15" s="26"/>
       <c r="O15" s="21"/>
       <c r="P15" s="24"/>
-      <c r="Q15" s="22"/>
+      <c r="Q15" s="70" t="s">
+        <v>71</v>
+      </c>
       <c r="R15" s="24"/>
       <c r="S15" s="24"/>
       <c r="T15" s="24"/>
@@ -2459,16 +2478,16 @@
     </row>
     <row r="16" spans="1:26" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="7"/>
-      <c r="B16" s="93"/>
-      <c r="C16" s="95" t="s">
+      <c r="B16" s="92"/>
+      <c r="C16" s="94" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="96"/>
+      <c r="D16" s="95"/>
       <c r="E16" s="27"/>
       <c r="F16" s="28"/>
       <c r="G16" s="23"/>
-      <c r="H16" s="72" t="s">
-        <v>72</v>
+      <c r="H16" s="70" t="s">
+        <v>71</v>
       </c>
       <c r="I16" s="24"/>
       <c r="J16" s="22"/>
@@ -2491,11 +2510,11 @@
     </row>
     <row r="17" spans="1:27" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="7"/>
-      <c r="B17" s="94"/>
-      <c r="C17" s="97" t="s">
+      <c r="B17" s="93"/>
+      <c r="C17" s="96" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="98"/>
+      <c r="D17" s="97"/>
       <c r="E17" s="29"/>
       <c r="F17" s="30"/>
       <c r="G17" s="31"/>
@@ -2549,23 +2568,23 @@
     </row>
     <row r="19" spans="1:27" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B19" s="22"/>
-      <c r="C19" s="73" t="s">
+      <c r="C19" s="72" t="s">
         <v>34</v>
       </c>
-      <c r="D19" s="74"/>
-      <c r="E19" s="74"/>
-      <c r="F19" s="74"/>
-      <c r="G19" s="74"/>
-      <c r="H19" s="74"/>
-      <c r="I19" s="74"/>
-      <c r="J19" s="74"/>
-      <c r="L19" s="62"/>
-      <c r="M19" s="61"/>
-      <c r="N19" s="64" t="s">
+      <c r="D19" s="73"/>
+      <c r="E19" s="73"/>
+      <c r="F19" s="73"/>
+      <c r="G19" s="73"/>
+      <c r="H19" s="73"/>
+      <c r="I19" s="73"/>
+      <c r="J19" s="73"/>
+      <c r="L19" s="61"/>
+      <c r="M19" s="60"/>
+      <c r="N19" s="63" t="s">
         <v>60</v>
       </c>
-      <c r="O19" s="61"/>
-      <c r="P19" s="63"/>
+      <c r="O19" s="60"/>
+      <c r="P19" s="62"/>
       <c r="Q19" s="56" t="s">
         <v>53</v>
       </c>
@@ -2588,23 +2607,23 @@
     </row>
     <row r="21" spans="1:27" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="24"/>
-      <c r="C21" s="73" t="s">
+      <c r="C21" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="D21" s="74"/>
-      <c r="E21" s="74"/>
-      <c r="F21" s="74"/>
-      <c r="G21" s="74"/>
-      <c r="H21" s="74"/>
-      <c r="I21" s="74"/>
-      <c r="J21" s="74"/>
-      <c r="M21" s="84" t="s">
+      <c r="D21" s="73"/>
+      <c r="E21" s="73"/>
+      <c r="F21" s="73"/>
+      <c r="G21" s="73"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="73"/>
+      <c r="J21" s="73"/>
+      <c r="M21" s="83" t="s">
         <v>63</v>
       </c>
-      <c r="N21" s="114" t="s">
+      <c r="N21" s="113" t="s">
         <v>63</v>
       </c>
-      <c r="O21" s="116" t="s">
+      <c r="O21" s="115" t="s">
         <v>63</v>
       </c>
       <c r="Q21"/>
@@ -2619,9 +2638,9 @@
       <c r="H22" s="55"/>
       <c r="I22" s="55"/>
       <c r="J22" s="55"/>
-      <c r="M22" s="85"/>
-      <c r="N22" s="115"/>
-      <c r="O22" s="117"/>
+      <c r="M22" s="84"/>
+      <c r="N22" s="114"/>
+      <c r="O22" s="116"/>
       <c r="Q22" s="56" t="s">
         <v>55</v>
       </c>
@@ -2629,24 +2648,24 @@
     </row>
     <row r="23" spans="1:27" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="23"/>
-      <c r="C23" s="73" t="s">
+      <c r="C23" s="72" t="s">
         <v>38</v>
       </c>
-      <c r="D23" s="74"/>
-      <c r="E23" s="74"/>
-      <c r="F23" s="74"/>
-      <c r="G23" s="74"/>
-      <c r="H23" s="74"/>
-      <c r="I23" s="74"/>
-      <c r="J23" s="74"/>
+      <c r="D23" s="73"/>
+      <c r="E23" s="73"/>
+      <c r="F23" s="73"/>
+      <c r="G23" s="73"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73"/>
+      <c r="J23" s="73"/>
       <c r="K23" s="56"/>
-      <c r="M23" s="118" t="s">
+      <c r="M23" s="117" t="s">
         <v>35</v>
       </c>
-      <c r="N23" s="120" t="s">
+      <c r="N23" s="119" t="s">
         <v>36</v>
       </c>
-      <c r="O23" s="118" t="s">
+      <c r="O23" s="117" t="s">
         <v>37</v>
       </c>
       <c r="AA23" s="10"/>
@@ -2654,9 +2673,9 @@
     <row r="24" spans="1:27" x14ac:dyDescent="0.35">
       <c r="K24" s="56"/>
       <c r="L24"/>
-      <c r="M24" s="119"/>
-      <c r="N24" s="119"/>
-      <c r="O24" s="119"/>
+      <c r="M24" s="118"/>
+      <c r="N24" s="118"/>
+      <c r="O24" s="118"/>
       <c r="P24"/>
       <c r="AA24" s="10"/>
     </row>
@@ -2727,351 +2746,351 @@
   <sheetData>
     <row r="1" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="120" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="121"/>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
-      <c r="L2" s="121"/>
-      <c r="M2" s="121"/>
-      <c r="N2" s="121"/>
+      <c r="C2" s="120"/>
+      <c r="D2" s="120"/>
+      <c r="E2" s="120"/>
+      <c r="F2" s="120"/>
+      <c r="G2" s="120"/>
+      <c r="H2" s="120"/>
+      <c r="I2" s="120"/>
+      <c r="J2" s="120"/>
+      <c r="K2" s="120"/>
+      <c r="L2" s="120"/>
+      <c r="M2" s="120"/>
+      <c r="N2" s="120"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B3" s="122"/>
-      <c r="C3" s="122"/>
-      <c r="D3" s="122"/>
-      <c r="E3" s="122"/>
-      <c r="F3" s="122"/>
-      <c r="G3" s="122"/>
-      <c r="H3" s="122"/>
-      <c r="I3" s="122"/>
-      <c r="J3" s="122"/>
-      <c r="K3" s="122"/>
-      <c r="L3" s="122"/>
-      <c r="M3" s="122"/>
-      <c r="N3" s="122"/>
+      <c r="B3" s="121"/>
+      <c r="C3" s="121"/>
+      <c r="D3" s="121"/>
+      <c r="E3" s="121"/>
+      <c r="F3" s="121"/>
+      <c r="G3" s="121"/>
+      <c r="H3" s="121"/>
+      <c r="I3" s="121"/>
+      <c r="J3" s="121"/>
+      <c r="K3" s="121"/>
+      <c r="L3" s="121"/>
+      <c r="M3" s="121"/>
+      <c r="N3" s="121"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B4" s="122"/>
-      <c r="C4" s="122"/>
-      <c r="D4" s="122"/>
-      <c r="E4" s="122"/>
-      <c r="F4" s="122"/>
-      <c r="G4" s="122"/>
-      <c r="H4" s="122"/>
-      <c r="I4" s="122"/>
-      <c r="J4" s="122"/>
-      <c r="K4" s="122"/>
-      <c r="L4" s="122"/>
-      <c r="M4" s="122"/>
-      <c r="N4" s="122"/>
+      <c r="B4" s="121"/>
+      <c r="C4" s="121"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="121"/>
+      <c r="L4" s="121"/>
+      <c r="M4" s="121"/>
+      <c r="N4" s="121"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B5" s="122"/>
-      <c r="C5" s="122"/>
-      <c r="D5" s="122"/>
-      <c r="E5" s="122"/>
-      <c r="F5" s="122"/>
-      <c r="G5" s="122"/>
-      <c r="H5" s="122"/>
-      <c r="I5" s="122"/>
-      <c r="J5" s="122"/>
-      <c r="K5" s="122"/>
-      <c r="L5" s="122"/>
-      <c r="M5" s="122"/>
-      <c r="N5" s="122"/>
+      <c r="B5" s="121"/>
+      <c r="C5" s="121"/>
+      <c r="D5" s="121"/>
+      <c r="E5" s="121"/>
+      <c r="F5" s="121"/>
+      <c r="G5" s="121"/>
+      <c r="H5" s="121"/>
+      <c r="I5" s="121"/>
+      <c r="J5" s="121"/>
+      <c r="K5" s="121"/>
+      <c r="L5" s="121"/>
+      <c r="M5" s="121"/>
+      <c r="N5" s="121"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B6" s="122"/>
-      <c r="C6" s="122"/>
-      <c r="D6" s="122"/>
-      <c r="E6" s="122"/>
-      <c r="F6" s="122"/>
-      <c r="G6" s="122"/>
-      <c r="H6" s="122"/>
-      <c r="I6" s="122"/>
-      <c r="J6" s="122"/>
-      <c r="K6" s="122"/>
-      <c r="L6" s="122"/>
-      <c r="M6" s="122"/>
-      <c r="N6" s="122"/>
+      <c r="B6" s="121"/>
+      <c r="C6" s="121"/>
+      <c r="D6" s="121"/>
+      <c r="E6" s="121"/>
+      <c r="F6" s="121"/>
+      <c r="G6" s="121"/>
+      <c r="H6" s="121"/>
+      <c r="I6" s="121"/>
+      <c r="J6" s="121"/>
+      <c r="K6" s="121"/>
+      <c r="L6" s="121"/>
+      <c r="M6" s="121"/>
+      <c r="N6" s="121"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B7" s="122"/>
-      <c r="C7" s="122"/>
-      <c r="D7" s="122"/>
-      <c r="E7" s="122"/>
-      <c r="F7" s="122"/>
-      <c r="G7" s="122"/>
-      <c r="H7" s="122"/>
-      <c r="I7" s="122"/>
-      <c r="J7" s="122"/>
-      <c r="K7" s="122"/>
-      <c r="L7" s="122"/>
-      <c r="M7" s="122"/>
-      <c r="N7" s="122"/>
+      <c r="B7" s="121"/>
+      <c r="C7" s="121"/>
+      <c r="D7" s="121"/>
+      <c r="E7" s="121"/>
+      <c r="F7" s="121"/>
+      <c r="G7" s="121"/>
+      <c r="H7" s="121"/>
+      <c r="I7" s="121"/>
+      <c r="J7" s="121"/>
+      <c r="K7" s="121"/>
+      <c r="L7" s="121"/>
+      <c r="M7" s="121"/>
+      <c r="N7" s="121"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B8" s="122"/>
-      <c r="C8" s="122"/>
-      <c r="D8" s="122"/>
-      <c r="E8" s="122"/>
-      <c r="F8" s="122"/>
-      <c r="G8" s="122"/>
-      <c r="H8" s="122"/>
-      <c r="I8" s="122"/>
-      <c r="J8" s="122"/>
-      <c r="K8" s="122"/>
-      <c r="L8" s="122"/>
-      <c r="M8" s="122"/>
-      <c r="N8" s="122"/>
+      <c r="B8" s="121"/>
+      <c r="C8" s="121"/>
+      <c r="D8" s="121"/>
+      <c r="E8" s="121"/>
+      <c r="F8" s="121"/>
+      <c r="G8" s="121"/>
+      <c r="H8" s="121"/>
+      <c r="I8" s="121"/>
+      <c r="J8" s="121"/>
+      <c r="K8" s="121"/>
+      <c r="L8" s="121"/>
+      <c r="M8" s="121"/>
+      <c r="N8" s="121"/>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B9" s="122"/>
-      <c r="C9" s="122"/>
-      <c r="D9" s="122"/>
-      <c r="E9" s="122"/>
-      <c r="F9" s="122"/>
-      <c r="G9" s="122"/>
-      <c r="H9" s="122"/>
-      <c r="I9" s="122"/>
-      <c r="J9" s="122"/>
-      <c r="K9" s="122"/>
-      <c r="L9" s="122"/>
-      <c r="M9" s="122"/>
-      <c r="N9" s="122"/>
+      <c r="B9" s="121"/>
+      <c r="C9" s="121"/>
+      <c r="D9" s="121"/>
+      <c r="E9" s="121"/>
+      <c r="F9" s="121"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="121"/>
+      <c r="I9" s="121"/>
+      <c r="J9" s="121"/>
+      <c r="K9" s="121"/>
+      <c r="L9" s="121"/>
+      <c r="M9" s="121"/>
+      <c r="N9" s="121"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B10" s="122"/>
-      <c r="C10" s="122"/>
-      <c r="D10" s="122"/>
-      <c r="E10" s="122"/>
-      <c r="F10" s="122"/>
-      <c r="G10" s="122"/>
-      <c r="H10" s="122"/>
-      <c r="I10" s="122"/>
-      <c r="J10" s="122"/>
-      <c r="K10" s="122"/>
-      <c r="L10" s="122"/>
-      <c r="M10" s="122"/>
-      <c r="N10" s="122"/>
+      <c r="B10" s="121"/>
+      <c r="C10" s="121"/>
+      <c r="D10" s="121"/>
+      <c r="E10" s="121"/>
+      <c r="F10" s="121"/>
+      <c r="G10" s="121"/>
+      <c r="H10" s="121"/>
+      <c r="I10" s="121"/>
+      <c r="J10" s="121"/>
+      <c r="K10" s="121"/>
+      <c r="L10" s="121"/>
+      <c r="M10" s="121"/>
+      <c r="N10" s="121"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B11" s="122"/>
-      <c r="C11" s="122"/>
-      <c r="D11" s="122"/>
-      <c r="E11" s="122"/>
-      <c r="F11" s="122"/>
-      <c r="G11" s="122"/>
-      <c r="H11" s="122"/>
-      <c r="I11" s="122"/>
-      <c r="J11" s="122"/>
-      <c r="K11" s="122"/>
-      <c r="L11" s="122"/>
-      <c r="M11" s="122"/>
-      <c r="N11" s="122"/>
+      <c r="B11" s="121"/>
+      <c r="C11" s="121"/>
+      <c r="D11" s="121"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="121"/>
+      <c r="H11" s="121"/>
+      <c r="I11" s="121"/>
+      <c r="J11" s="121"/>
+      <c r="K11" s="121"/>
+      <c r="L11" s="121"/>
+      <c r="M11" s="121"/>
+      <c r="N11" s="121"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B12" s="122"/>
-      <c r="C12" s="122"/>
-      <c r="D12" s="122"/>
-      <c r="E12" s="122"/>
-      <c r="F12" s="122"/>
-      <c r="G12" s="122"/>
-      <c r="H12" s="122"/>
-      <c r="I12" s="122"/>
-      <c r="J12" s="122"/>
-      <c r="K12" s="122"/>
-      <c r="L12" s="122"/>
-      <c r="M12" s="122"/>
-      <c r="N12" s="122"/>
+      <c r="B12" s="121"/>
+      <c r="C12" s="121"/>
+      <c r="D12" s="121"/>
+      <c r="E12" s="121"/>
+      <c r="F12" s="121"/>
+      <c r="G12" s="121"/>
+      <c r="H12" s="121"/>
+      <c r="I12" s="121"/>
+      <c r="J12" s="121"/>
+      <c r="K12" s="121"/>
+      <c r="L12" s="121"/>
+      <c r="M12" s="121"/>
+      <c r="N12" s="121"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B13" s="122"/>
-      <c r="C13" s="122"/>
-      <c r="D13" s="122"/>
-      <c r="E13" s="122"/>
-      <c r="F13" s="122"/>
-      <c r="G13" s="122"/>
-      <c r="H13" s="122"/>
-      <c r="I13" s="122"/>
-      <c r="J13" s="122"/>
-      <c r="K13" s="122"/>
-      <c r="L13" s="122"/>
-      <c r="M13" s="122"/>
-      <c r="N13" s="122"/>
+      <c r="B13" s="121"/>
+      <c r="C13" s="121"/>
+      <c r="D13" s="121"/>
+      <c r="E13" s="121"/>
+      <c r="F13" s="121"/>
+      <c r="G13" s="121"/>
+      <c r="H13" s="121"/>
+      <c r="I13" s="121"/>
+      <c r="J13" s="121"/>
+      <c r="K13" s="121"/>
+      <c r="L13" s="121"/>
+      <c r="M13" s="121"/>
+      <c r="N13" s="121"/>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B14" s="122"/>
-      <c r="C14" s="122"/>
-      <c r="D14" s="122"/>
-      <c r="E14" s="122"/>
-      <c r="F14" s="122"/>
-      <c r="G14" s="122"/>
-      <c r="H14" s="122"/>
-      <c r="I14" s="122"/>
-      <c r="J14" s="122"/>
-      <c r="K14" s="122"/>
-      <c r="L14" s="122"/>
-      <c r="M14" s="122"/>
-      <c r="N14" s="122"/>
+      <c r="B14" s="121"/>
+      <c r="C14" s="121"/>
+      <c r="D14" s="121"/>
+      <c r="E14" s="121"/>
+      <c r="F14" s="121"/>
+      <c r="G14" s="121"/>
+      <c r="H14" s="121"/>
+      <c r="I14" s="121"/>
+      <c r="J14" s="121"/>
+      <c r="K14" s="121"/>
+      <c r="L14" s="121"/>
+      <c r="M14" s="121"/>
+      <c r="N14" s="121"/>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B15" s="122"/>
-      <c r="C15" s="122"/>
-      <c r="D15" s="122"/>
-      <c r="E15" s="122"/>
-      <c r="F15" s="122"/>
-      <c r="G15" s="122"/>
-      <c r="H15" s="122"/>
-      <c r="I15" s="122"/>
-      <c r="J15" s="122"/>
-      <c r="K15" s="122"/>
-      <c r="L15" s="122"/>
-      <c r="M15" s="122"/>
-      <c r="N15" s="122"/>
+      <c r="B15" s="121"/>
+      <c r="C15" s="121"/>
+      <c r="D15" s="121"/>
+      <c r="E15" s="121"/>
+      <c r="F15" s="121"/>
+      <c r="G15" s="121"/>
+      <c r="H15" s="121"/>
+      <c r="I15" s="121"/>
+      <c r="J15" s="121"/>
+      <c r="K15" s="121"/>
+      <c r="L15" s="121"/>
+      <c r="M15" s="121"/>
+      <c r="N15" s="121"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B16" s="122"/>
-      <c r="C16" s="122"/>
-      <c r="D16" s="122"/>
-      <c r="E16" s="122"/>
-      <c r="F16" s="122"/>
-      <c r="G16" s="122"/>
-      <c r="H16" s="122"/>
-      <c r="I16" s="122"/>
-      <c r="J16" s="122"/>
-      <c r="K16" s="122"/>
-      <c r="L16" s="122"/>
-      <c r="M16" s="122"/>
-      <c r="N16" s="122"/>
+      <c r="B16" s="121"/>
+      <c r="C16" s="121"/>
+      <c r="D16" s="121"/>
+      <c r="E16" s="121"/>
+      <c r="F16" s="121"/>
+      <c r="G16" s="121"/>
+      <c r="H16" s="121"/>
+      <c r="I16" s="121"/>
+      <c r="J16" s="121"/>
+      <c r="K16" s="121"/>
+      <c r="L16" s="121"/>
+      <c r="M16" s="121"/>
+      <c r="N16" s="121"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B17" s="122"/>
-      <c r="C17" s="122"/>
-      <c r="D17" s="122"/>
-      <c r="E17" s="122"/>
-      <c r="F17" s="122"/>
-      <c r="G17" s="122"/>
-      <c r="H17" s="122"/>
-      <c r="I17" s="122"/>
-      <c r="J17" s="122"/>
-      <c r="K17" s="122"/>
-      <c r="L17" s="122"/>
-      <c r="M17" s="122"/>
-      <c r="N17" s="122"/>
+      <c r="B17" s="121"/>
+      <c r="C17" s="121"/>
+      <c r="D17" s="121"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="121"/>
+      <c r="G17" s="121"/>
+      <c r="H17" s="121"/>
+      <c r="I17" s="121"/>
+      <c r="J17" s="121"/>
+      <c r="K17" s="121"/>
+      <c r="L17" s="121"/>
+      <c r="M17" s="121"/>
+      <c r="N17" s="121"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B18" s="122"/>
-      <c r="C18" s="122"/>
-      <c r="D18" s="122"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="122"/>
-      <c r="G18" s="122"/>
-      <c r="H18" s="122"/>
-      <c r="I18" s="122"/>
-      <c r="J18" s="122"/>
-      <c r="K18" s="122"/>
-      <c r="L18" s="122"/>
-      <c r="M18" s="122"/>
-      <c r="N18" s="122"/>
+      <c r="B18" s="121"/>
+      <c r="C18" s="121"/>
+      <c r="D18" s="121"/>
+      <c r="E18" s="121"/>
+      <c r="F18" s="121"/>
+      <c r="G18" s="121"/>
+      <c r="H18" s="121"/>
+      <c r="I18" s="121"/>
+      <c r="J18" s="121"/>
+      <c r="K18" s="121"/>
+      <c r="L18" s="121"/>
+      <c r="M18" s="121"/>
+      <c r="N18" s="121"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B19" s="122"/>
-      <c r="C19" s="122"/>
-      <c r="D19" s="122"/>
-      <c r="E19" s="122"/>
-      <c r="F19" s="122"/>
-      <c r="G19" s="122"/>
-      <c r="H19" s="122"/>
-      <c r="I19" s="122"/>
-      <c r="J19" s="122"/>
-      <c r="K19" s="122"/>
-      <c r="L19" s="122"/>
-      <c r="M19" s="122"/>
-      <c r="N19" s="122"/>
+      <c r="B19" s="121"/>
+      <c r="C19" s="121"/>
+      <c r="D19" s="121"/>
+      <c r="E19" s="121"/>
+      <c r="F19" s="121"/>
+      <c r="G19" s="121"/>
+      <c r="H19" s="121"/>
+      <c r="I19" s="121"/>
+      <c r="J19" s="121"/>
+      <c r="K19" s="121"/>
+      <c r="L19" s="121"/>
+      <c r="M19" s="121"/>
+      <c r="N19" s="121"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B20" s="122"/>
-      <c r="C20" s="122"/>
-      <c r="D20" s="122"/>
-      <c r="E20" s="122"/>
-      <c r="F20" s="122"/>
-      <c r="G20" s="122"/>
-      <c r="H20" s="122"/>
-      <c r="I20" s="122"/>
-      <c r="J20" s="122"/>
-      <c r="K20" s="122"/>
-      <c r="L20" s="122"/>
-      <c r="M20" s="122"/>
-      <c r="N20" s="122"/>
+      <c r="B20" s="121"/>
+      <c r="C20" s="121"/>
+      <c r="D20" s="121"/>
+      <c r="E20" s="121"/>
+      <c r="F20" s="121"/>
+      <c r="G20" s="121"/>
+      <c r="H20" s="121"/>
+      <c r="I20" s="121"/>
+      <c r="J20" s="121"/>
+      <c r="K20" s="121"/>
+      <c r="L20" s="121"/>
+      <c r="M20" s="121"/>
+      <c r="N20" s="121"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B21" s="122"/>
-      <c r="C21" s="122"/>
-      <c r="D21" s="122"/>
-      <c r="E21" s="122"/>
-      <c r="F21" s="122"/>
-      <c r="G21" s="122"/>
-      <c r="H21" s="122"/>
-      <c r="I21" s="122"/>
-      <c r="J21" s="122"/>
-      <c r="K21" s="122"/>
-      <c r="L21" s="122"/>
-      <c r="M21" s="122"/>
-      <c r="N21" s="122"/>
+      <c r="B21" s="121"/>
+      <c r="C21" s="121"/>
+      <c r="D21" s="121"/>
+      <c r="E21" s="121"/>
+      <c r="F21" s="121"/>
+      <c r="G21" s="121"/>
+      <c r="H21" s="121"/>
+      <c r="I21" s="121"/>
+      <c r="J21" s="121"/>
+      <c r="K21" s="121"/>
+      <c r="L21" s="121"/>
+      <c r="M21" s="121"/>
+      <c r="N21" s="121"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B22" s="122"/>
-      <c r="C22" s="122"/>
-      <c r="D22" s="122"/>
-      <c r="E22" s="122"/>
-      <c r="F22" s="122"/>
-      <c r="G22" s="122"/>
-      <c r="H22" s="122"/>
-      <c r="I22" s="122"/>
-      <c r="J22" s="122"/>
-      <c r="K22" s="122"/>
-      <c r="L22" s="122"/>
-      <c r="M22" s="122"/>
-      <c r="N22" s="122"/>
+      <c r="B22" s="121"/>
+      <c r="C22" s="121"/>
+      <c r="D22" s="121"/>
+      <c r="E22" s="121"/>
+      <c r="F22" s="121"/>
+      <c r="G22" s="121"/>
+      <c r="H22" s="121"/>
+      <c r="I22" s="121"/>
+      <c r="J22" s="121"/>
+      <c r="K22" s="121"/>
+      <c r="L22" s="121"/>
+      <c r="M22" s="121"/>
+      <c r="N22" s="121"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B23" s="122"/>
-      <c r="C23" s="122"/>
-      <c r="D23" s="122"/>
-      <c r="E23" s="122"/>
-      <c r="F23" s="122"/>
-      <c r="G23" s="122"/>
-      <c r="H23" s="122"/>
-      <c r="I23" s="122"/>
-      <c r="J23" s="122"/>
-      <c r="K23" s="122"/>
-      <c r="L23" s="122"/>
-      <c r="M23" s="122"/>
-      <c r="N23" s="122"/>
+      <c r="B23" s="121"/>
+      <c r="C23" s="121"/>
+      <c r="D23" s="121"/>
+      <c r="E23" s="121"/>
+      <c r="F23" s="121"/>
+      <c r="G23" s="121"/>
+      <c r="H23" s="121"/>
+      <c r="I23" s="121"/>
+      <c r="J23" s="121"/>
+      <c r="K23" s="121"/>
+      <c r="L23" s="121"/>
+      <c r="M23" s="121"/>
+      <c r="N23" s="121"/>
     </row>
     <row r="24" spans="2:14" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="122"/>
-      <c r="C24" s="122"/>
-      <c r="D24" s="122"/>
-      <c r="E24" s="122"/>
-      <c r="F24" s="122"/>
-      <c r="G24" s="122"/>
-      <c r="H24" s="122"/>
-      <c r="I24" s="122"/>
-      <c r="J24" s="122"/>
-      <c r="K24" s="122"/>
-      <c r="L24" s="122"/>
-      <c r="M24" s="122"/>
-      <c r="N24" s="122"/>
+      <c r="B24" s="121"/>
+      <c r="C24" s="121"/>
+      <c r="D24" s="121"/>
+      <c r="E24" s="121"/>
+      <c r="F24" s="121"/>
+      <c r="G24" s="121"/>
+      <c r="H24" s="121"/>
+      <c r="I24" s="121"/>
+      <c r="J24" s="121"/>
+      <c r="K24" s="121"/>
+      <c r="L24" s="121"/>
+      <c r="M24" s="121"/>
+      <c r="N24" s="121"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/doc/AI-S4_portfoliomatrix.xlsx
+++ b/doc/AI-S4_portfoliomatrix.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mathi\Documents\hu\S4\ai-s4_student\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E40EF0D9-C7C3-46C3-9D82-8289C68748FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99AE50D7-9DBB-4C15-A9F6-54B6321DFB7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{9145D055-8147-4D48-BED2-085A2CF38ACC}"/>
+    <workbookView xWindow="-28920" yWindow="7995" windowWidth="29040" windowHeight="15720" xr2:uid="{9145D055-8147-4D48-BED2-085A2CF38ACC}"/>
   </bookViews>
   <sheets>
     <sheet name="AI-S4" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="74">
   <si>
     <t>Leeruitkomsten</t>
   </si>
@@ -396,6 +396,12 @@
   </si>
   <si>
     <t>X</t>
+  </si>
+  <si>
+    <t>Beoordelingsdocument</t>
+  </si>
+  <si>
+    <t>23/06/2026</t>
   </si>
 </sst>
 </file>
@@ -1200,7 +1206,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" textRotation="90"/>
@@ -1270,9 +1276,6 @@
     <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1294,9 +1297,6 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1312,9 +1312,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1327,9 +1324,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1387,45 +1381,144 @@
     <xf numFmtId="0" fontId="9" fillId="14" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -1450,119 +1543,20 @@
     <xf numFmtId="0" fontId="10" fillId="13" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2031,71 +2025,71 @@
     </row>
     <row r="4" spans="1:26" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7"/>
-      <c r="B4" s="57" t="s">
+      <c r="B4" s="53" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>70</v>
       </c>
       <c r="D4" s="13"/>
-      <c r="E4" s="81" t="s">
+      <c r="E4" s="110" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="79" t="s">
+      <c r="F4" s="108" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="79" t="s">
+      <c r="G4" s="108" t="s">
         <v>65</v>
       </c>
-      <c r="H4" s="79" t="s">
+      <c r="H4" s="108" t="s">
         <v>67</v>
       </c>
-      <c r="I4" s="79" t="s">
+      <c r="I4" s="108" t="s">
         <v>68</v>
       </c>
-      <c r="J4" s="79" t="s">
+      <c r="J4" s="108" t="s">
         <v>66</v>
       </c>
-      <c r="K4" s="79" t="s">
+      <c r="K4" s="108" t="s">
         <v>69</v>
       </c>
-      <c r="L4" s="79" t="s">
+      <c r="L4" s="108" t="s">
         <v>4</v>
       </c>
-      <c r="M4" s="79" t="s">
+      <c r="M4" s="108" t="s">
         <v>5</v>
       </c>
-      <c r="N4" s="77" t="s">
+      <c r="N4" s="106" t="s">
         <v>6</v>
       </c>
-      <c r="O4" s="88" t="s">
+      <c r="O4" s="98" t="s">
         <v>28</v>
       </c>
-      <c r="P4" s="74" t="s">
+      <c r="P4" s="101" t="s">
         <v>29</v>
       </c>
-      <c r="Q4" s="74" t="s">
+      <c r="Q4" s="101" t="s">
         <v>30</v>
       </c>
-      <c r="R4" s="74" t="s">
+      <c r="R4" s="101" t="s">
         <v>15</v>
       </c>
-      <c r="S4" s="74" t="s">
+      <c r="S4" s="101" t="s">
         <v>16</v>
       </c>
-      <c r="T4" s="74" t="s">
+      <c r="T4" s="101" t="s">
         <v>17</v>
       </c>
-      <c r="U4" s="74" t="s">
+      <c r="U4" s="101" t="s">
         <v>58</v>
       </c>
-      <c r="V4" s="74" t="s">
+      <c r="V4" s="101" t="s">
         <v>56</v>
       </c>
-      <c r="W4" s="74" t="s">
+      <c r="W4" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="X4" s="85" t="s">
+      <c r="X4" s="95" t="s">
         <v>31</v>
       </c>
       <c r="Y4" s="9"/>
@@ -2103,65 +2097,65 @@
     </row>
     <row r="5" spans="1:26" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7"/>
-      <c r="B5" s="58" t="s">
+      <c r="B5" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="122">
-        <v>46147</v>
+      <c r="C5" s="65" t="s">
+        <v>73</v>
       </c>
       <c r="D5" s="16"/>
-      <c r="E5" s="82"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="80"/>
-      <c r="K5" s="80"/>
-      <c r="L5" s="80"/>
-      <c r="M5" s="80"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="89"/>
-      <c r="P5" s="75"/>
-      <c r="Q5" s="75"/>
-      <c r="R5" s="75"/>
-      <c r="S5" s="75"/>
-      <c r="T5" s="75"/>
-      <c r="U5" s="75"/>
-      <c r="V5" s="75"/>
-      <c r="W5" s="75"/>
-      <c r="X5" s="86"/>
+      <c r="E5" s="111"/>
+      <c r="F5" s="109"/>
+      <c r="G5" s="109"/>
+      <c r="H5" s="109"/>
+      <c r="I5" s="109"/>
+      <c r="J5" s="109"/>
+      <c r="K5" s="109"/>
+      <c r="L5" s="109"/>
+      <c r="M5" s="109"/>
+      <c r="N5" s="107"/>
+      <c r="O5" s="99"/>
+      <c r="P5" s="102"/>
+      <c r="Q5" s="102"/>
+      <c r="R5" s="102"/>
+      <c r="S5" s="102"/>
+      <c r="T5" s="102"/>
+      <c r="U5" s="102"/>
+      <c r="V5" s="102"/>
+      <c r="W5" s="102"/>
+      <c r="X5" s="96"/>
       <c r="Y5" s="9"/>
       <c r="Z5"/>
     </row>
     <row r="6" spans="1:26" ht="50.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="7"/>
-      <c r="B6" s="59" t="s">
+      <c r="B6" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="15">
-        <v>2</v>
+      <c r="C6" s="15" t="s">
+        <v>72</v>
       </c>
       <c r="D6" s="16"/>
-      <c r="E6" s="82"/>
-      <c r="F6" s="80"/>
-      <c r="G6" s="80"/>
-      <c r="H6" s="80"/>
-      <c r="I6" s="80"/>
-      <c r="J6" s="80"/>
-      <c r="K6" s="80"/>
-      <c r="L6" s="80"/>
-      <c r="M6" s="80"/>
-      <c r="N6" s="78"/>
-      <c r="O6" s="89"/>
-      <c r="P6" s="75"/>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="75"/>
-      <c r="S6" s="75"/>
-      <c r="T6" s="75"/>
-      <c r="U6" s="75"/>
-      <c r="V6" s="75"/>
-      <c r="W6" s="75"/>
-      <c r="X6" s="86"/>
+      <c r="E6" s="111"/>
+      <c r="F6" s="109"/>
+      <c r="G6" s="109"/>
+      <c r="H6" s="109"/>
+      <c r="I6" s="109"/>
+      <c r="J6" s="109"/>
+      <c r="K6" s="109"/>
+      <c r="L6" s="109"/>
+      <c r="M6" s="109"/>
+      <c r="N6" s="107"/>
+      <c r="O6" s="99"/>
+      <c r="P6" s="102"/>
+      <c r="Q6" s="102"/>
+      <c r="R6" s="102"/>
+      <c r="S6" s="102"/>
+      <c r="T6" s="102"/>
+      <c r="U6" s="102"/>
+      <c r="V6" s="102"/>
+      <c r="W6" s="102"/>
+      <c r="X6" s="96"/>
       <c r="Y6" s="9"/>
       <c r="Z6"/>
     </row>
@@ -2170,173 +2164,213 @@
       <c r="B7" s="2"/>
       <c r="C7" s="4"/>
       <c r="D7" s="5"/>
-      <c r="E7" s="82"/>
-      <c r="F7" s="80"/>
-      <c r="G7" s="80"/>
-      <c r="H7" s="80"/>
-      <c r="I7" s="80"/>
-      <c r="J7" s="80"/>
-      <c r="K7" s="80"/>
-      <c r="L7" s="80"/>
-      <c r="M7" s="80"/>
-      <c r="N7" s="78"/>
-      <c r="O7" s="90"/>
-      <c r="P7" s="76"/>
-      <c r="Q7" s="76"/>
-      <c r="R7" s="76"/>
-      <c r="S7" s="76"/>
-      <c r="T7" s="76"/>
-      <c r="U7" s="76"/>
-      <c r="V7" s="76"/>
-      <c r="W7" s="76"/>
-      <c r="X7" s="87"/>
+      <c r="E7" s="111"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="109"/>
+      <c r="H7" s="109"/>
+      <c r="I7" s="109"/>
+      <c r="J7" s="109"/>
+      <c r="K7" s="109"/>
+      <c r="L7" s="109"/>
+      <c r="M7" s="109"/>
+      <c r="N7" s="107"/>
+      <c r="O7" s="100"/>
+      <c r="P7" s="103"/>
+      <c r="Q7" s="103"/>
+      <c r="R7" s="103"/>
+      <c r="S7" s="103"/>
+      <c r="T7" s="103"/>
+      <c r="U7" s="103"/>
+      <c r="V7" s="103"/>
+      <c r="W7" s="103"/>
+      <c r="X7" s="97"/>
       <c r="Y7" s="2"/>
     </row>
     <row r="8" spans="1:26" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="7"/>
-      <c r="B8" s="110" t="s">
+      <c r="B8" s="92" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="98" t="s">
+      <c r="C8" s="80" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="99"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="37"/>
-      <c r="K8" s="36"/>
-      <c r="L8" s="36"/>
-      <c r="M8" s="37"/>
-      <c r="N8" s="38"/>
-      <c r="O8" s="37"/>
-      <c r="P8" s="37"/>
-      <c r="Q8" s="71" t="s">
-        <v>71</v>
-      </c>
-      <c r="R8" s="37"/>
-      <c r="S8" s="37"/>
-      <c r="T8" s="37"/>
-      <c r="U8" s="37"/>
-      <c r="V8" s="37"/>
-      <c r="W8" s="39"/>
-      <c r="X8" s="40"/>
+      <c r="D8" s="81"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="34"/>
+      <c r="L8" s="34"/>
+      <c r="M8" s="35"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="35"/>
+      <c r="P8" s="116" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q8" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="R8" s="35"/>
+      <c r="S8" s="35"/>
+      <c r="T8" s="35"/>
+      <c r="U8" s="35"/>
+      <c r="V8" s="35"/>
+      <c r="W8" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="X8" s="37"/>
       <c r="Y8" s="7"/>
       <c r="Z8"/>
     </row>
     <row r="9" spans="1:26" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="7"/>
-      <c r="B9" s="111"/>
-      <c r="C9" s="100" t="s">
+      <c r="B9" s="93"/>
+      <c r="C9" s="82" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="101"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="42"/>
-      <c r="J9" s="42"/>
-      <c r="K9" s="42"/>
-      <c r="L9" s="42"/>
-      <c r="M9" s="42"/>
-      <c r="N9" s="43"/>
-      <c r="O9" s="71" t="s">
-        <v>71</v>
-      </c>
-      <c r="P9" s="64"/>
-      <c r="Q9" s="71" t="s">
-        <v>71</v>
-      </c>
-      <c r="R9" s="44"/>
-      <c r="S9" s="44"/>
-      <c r="T9" s="44"/>
-      <c r="U9" s="44"/>
-      <c r="V9" s="44"/>
-      <c r="W9" s="42"/>
-      <c r="X9" s="43"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="39"/>
+      <c r="J9" s="39"/>
+      <c r="K9" s="39"/>
+      <c r="L9" s="39"/>
+      <c r="M9" s="39"/>
+      <c r="N9" s="40"/>
+      <c r="O9" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="P9" s="117" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q9" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="R9" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="S9" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="T9" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="U9" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="V9" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="W9" s="39"/>
+      <c r="X9" s="40"/>
       <c r="Y9" s="7"/>
       <c r="Z9"/>
     </row>
     <row r="10" spans="1:26" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="7"/>
-      <c r="B10" s="111"/>
-      <c r="C10" s="102" t="s">
+      <c r="B10" s="93"/>
+      <c r="C10" s="84" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="103"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="42"/>
-      <c r="K10" s="42"/>
-      <c r="L10" s="42"/>
-      <c r="M10" s="42"/>
-      <c r="N10" s="43"/>
-      <c r="O10" s="71" t="s">
-        <v>71</v>
-      </c>
-      <c r="P10" s="64"/>
-      <c r="Q10" s="71" t="s">
-        <v>71</v>
-      </c>
-      <c r="R10" s="44"/>
-      <c r="S10" s="44"/>
-      <c r="T10" s="44"/>
-      <c r="U10" s="44"/>
-      <c r="V10" s="44"/>
-      <c r="W10" s="44"/>
-      <c r="X10" s="45"/>
+      <c r="D10" s="85"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="39"/>
+      <c r="K10" s="39"/>
+      <c r="L10" s="39"/>
+      <c r="M10" s="39"/>
+      <c r="N10" s="40"/>
+      <c r="O10" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="P10" s="117" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q10" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="R10" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="S10" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="T10" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="U10" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="V10" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="W10" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="X10" s="41"/>
       <c r="Y10" s="7"/>
       <c r="Z10"/>
     </row>
     <row r="11" spans="1:26" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="7"/>
-      <c r="B11" s="112"/>
-      <c r="C11" s="104" t="s">
+      <c r="B11" s="94"/>
+      <c r="C11" s="86" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="105"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="47"/>
-      <c r="G11" s="47"/>
-      <c r="H11" s="47"/>
-      <c r="I11" s="47"/>
-      <c r="J11" s="47"/>
-      <c r="K11" s="47"/>
-      <c r="L11" s="47"/>
-      <c r="M11" s="47"/>
-      <c r="N11" s="48"/>
-      <c r="O11" s="71" t="s">
-        <v>71</v>
-      </c>
-      <c r="P11" s="49"/>
-      <c r="Q11" s="71" t="s">
-        <v>71</v>
-      </c>
-      <c r="R11" s="69"/>
-      <c r="S11" s="69"/>
-      <c r="T11" s="69"/>
-      <c r="U11" s="69"/>
-      <c r="V11" s="69"/>
-      <c r="W11" s="47"/>
-      <c r="X11" s="50"/>
+      <c r="D11" s="87"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="43"/>
+      <c r="K11" s="43"/>
+      <c r="L11" s="43"/>
+      <c r="M11" s="43"/>
+      <c r="N11" s="44"/>
+      <c r="O11" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="P11" s="45"/>
+      <c r="Q11" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="R11" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="S11" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="T11" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="U11" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="V11" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="W11" s="43"/>
+      <c r="X11" s="46"/>
       <c r="Y11" s="7"/>
       <c r="Z11"/>
     </row>
     <row r="12" spans="1:26" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="7"/>
-      <c r="B12" s="91" t="s">
+      <c r="B12" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="106" t="s">
+      <c r="C12" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="107"/>
+      <c r="D12" s="89"/>
       <c r="E12" s="17"/>
       <c r="F12" s="18"/>
       <c r="G12" s="18"/>
@@ -2347,154 +2381,182 @@
       <c r="L12" s="19"/>
       <c r="M12" s="18"/>
       <c r="N12" s="20"/>
-      <c r="O12" s="65"/>
-      <c r="P12" s="66"/>
-      <c r="Q12" s="70" t="s">
-        <v>71</v>
-      </c>
-      <c r="R12" s="66"/>
-      <c r="S12" s="65"/>
-      <c r="T12" s="65"/>
-      <c r="U12" s="65"/>
-      <c r="V12" s="66"/>
-      <c r="W12" s="67"/>
-      <c r="X12" s="68"/>
+      <c r="O12" s="118" t="s">
+        <v>71</v>
+      </c>
+      <c r="P12" s="61"/>
+      <c r="Q12" s="63" t="s">
+        <v>71</v>
+      </c>
+      <c r="R12" s="61"/>
+      <c r="S12" s="60"/>
+      <c r="T12" s="60"/>
+      <c r="U12" s="60"/>
+      <c r="V12" s="61"/>
+      <c r="W12" s="63" t="s">
+        <v>71</v>
+      </c>
+      <c r="X12" s="62"/>
       <c r="Y12" s="7"/>
       <c r="Z12"/>
     </row>
     <row r="13" spans="1:26" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="7"/>
-      <c r="B13" s="92"/>
-      <c r="C13" s="108" t="s">
+      <c r="B13" s="74"/>
+      <c r="C13" s="90" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="109"/>
+      <c r="D13" s="91"/>
       <c r="E13" s="21"/>
-      <c r="F13" s="70" t="s">
+      <c r="F13" s="63" t="s">
         <v>71</v>
       </c>
       <c r="G13" s="23"/>
       <c r="H13" s="24"/>
       <c r="I13" s="24"/>
       <c r="J13" s="22"/>
-      <c r="K13" s="70" t="s">
+      <c r="K13" s="63" t="s">
         <v>71</v>
       </c>
       <c r="L13" s="23"/>
       <c r="M13" s="24"/>
-      <c r="N13" s="25"/>
+      <c r="N13" s="63" t="s">
+        <v>71</v>
+      </c>
       <c r="O13" s="24"/>
       <c r="P13" s="23"/>
-      <c r="Q13" s="70" t="s">
+      <c r="Q13" s="63" t="s">
         <v>71</v>
       </c>
       <c r="R13" s="24"/>
       <c r="S13" s="24"/>
       <c r="T13" s="24"/>
       <c r="U13" s="24"/>
-      <c r="V13" s="22"/>
-      <c r="W13" s="22"/>
-      <c r="X13" s="26"/>
+      <c r="V13" s="63" t="s">
+        <v>71</v>
+      </c>
+      <c r="W13" s="63" t="s">
+        <v>71</v>
+      </c>
+      <c r="X13" s="25"/>
       <c r="Y13" s="7"/>
       <c r="Z13"/>
     </row>
     <row r="14" spans="1:26" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="7"/>
-      <c r="B14" s="92"/>
-      <c r="C14" s="94" t="s">
+      <c r="B14" s="74"/>
+      <c r="C14" s="76" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="95"/>
-      <c r="E14" s="70" t="s">
-        <v>71</v>
-      </c>
-      <c r="F14" s="70" t="s">
-        <v>71</v>
-      </c>
-      <c r="G14" s="70" t="s">
-        <v>71</v>
-      </c>
-      <c r="H14" s="70" t="s">
-        <v>71</v>
-      </c>
-      <c r="I14" s="70" t="s">
+      <c r="D14" s="77"/>
+      <c r="E14" s="63" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14" s="63" t="s">
+        <v>71</v>
+      </c>
+      <c r="G14" s="63" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" s="63" t="s">
+        <v>71</v>
+      </c>
+      <c r="I14" s="63" t="s">
         <v>71</v>
       </c>
       <c r="J14" s="24"/>
-      <c r="K14" s="70" t="s">
+      <c r="K14" s="63" t="s">
         <v>71</v>
       </c>
       <c r="L14" s="22"/>
       <c r="M14" s="24"/>
-      <c r="N14" s="25"/>
+      <c r="N14" s="63" t="s">
+        <v>71</v>
+      </c>
       <c r="O14" s="21"/>
-      <c r="P14" s="24"/>
-      <c r="Q14" s="70" t="s">
+      <c r="P14" s="118" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q14" s="63" t="s">
         <v>71</v>
       </c>
       <c r="R14" s="24"/>
       <c r="S14" s="24"/>
       <c r="T14" s="24"/>
       <c r="U14" s="24"/>
-      <c r="V14" s="22"/>
-      <c r="W14" s="22"/>
-      <c r="X14" s="26"/>
+      <c r="V14" s="63" t="s">
+        <v>71</v>
+      </c>
+      <c r="W14" s="63" t="s">
+        <v>71</v>
+      </c>
+      <c r="X14" s="25"/>
       <c r="Y14" s="7"/>
       <c r="Z14"/>
     </row>
     <row r="15" spans="1:26" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="7"/>
-      <c r="B15" s="92"/>
-      <c r="C15" s="94" t="s">
+      <c r="B15" s="74"/>
+      <c r="C15" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="95"/>
+      <c r="D15" s="77"/>
       <c r="E15" s="21"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="70" t="s">
+      <c r="H15" s="63" t="s">
         <v>71</v>
       </c>
       <c r="I15" s="23"/>
       <c r="J15" s="22"/>
       <c r="K15" s="23"/>
       <c r="L15" s="23"/>
-      <c r="M15" s="22"/>
-      <c r="N15" s="26"/>
+      <c r="M15" s="63" t="s">
+        <v>71</v>
+      </c>
+      <c r="N15" s="25"/>
       <c r="O15" s="21"/>
       <c r="P15" s="24"/>
-      <c r="Q15" s="70" t="s">
+      <c r="Q15" s="63" t="s">
         <v>71</v>
       </c>
       <c r="R15" s="24"/>
       <c r="S15" s="24"/>
       <c r="T15" s="24"/>
       <c r="U15" s="24"/>
-      <c r="V15" s="22"/>
-      <c r="W15" s="22"/>
-      <c r="X15" s="26"/>
+      <c r="V15" s="63" t="s">
+        <v>71</v>
+      </c>
+      <c r="W15" s="63" t="s">
+        <v>71</v>
+      </c>
+      <c r="X15" s="25"/>
       <c r="Y15" s="7"/>
       <c r="Z15"/>
     </row>
     <row r="16" spans="1:26" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="7"/>
-      <c r="B16" s="92"/>
-      <c r="C16" s="94" t="s">
+      <c r="B16" s="74"/>
+      <c r="C16" s="76" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="95"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="28"/>
+      <c r="D16" s="77"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="27"/>
       <c r="G16" s="23"/>
-      <c r="H16" s="70" t="s">
+      <c r="H16" s="63" t="s">
         <v>71</v>
       </c>
       <c r="I16" s="24"/>
       <c r="J16" s="22"/>
       <c r="K16" s="23"/>
       <c r="L16" s="23"/>
-      <c r="M16" s="22"/>
-      <c r="N16" s="25"/>
+      <c r="M16" s="63" t="s">
+        <v>71</v>
+      </c>
+      <c r="N16" s="63" t="s">
+        <v>71</v>
+      </c>
       <c r="O16" s="21"/>
       <c r="P16" s="23"/>
       <c r="Q16" s="23"/>
@@ -2502,39 +2564,45 @@
       <c r="S16" s="24"/>
       <c r="T16" s="24"/>
       <c r="U16" s="24"/>
-      <c r="V16" s="22"/>
-      <c r="W16" s="22"/>
-      <c r="X16" s="26"/>
+      <c r="V16" s="63" t="s">
+        <v>71</v>
+      </c>
+      <c r="W16" s="63" t="s">
+        <v>71</v>
+      </c>
+      <c r="X16" s="25"/>
       <c r="Y16" s="7"/>
       <c r="Z16"/>
     </row>
     <row r="17" spans="1:27" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="7"/>
-      <c r="B17" s="93"/>
-      <c r="C17" s="96" t="s">
+      <c r="B17" s="75"/>
+      <c r="C17" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="97"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="31"/>
-      <c r="I17" s="30"/>
-      <c r="J17" s="31"/>
-      <c r="K17" s="30"/>
-      <c r="L17" s="30"/>
-      <c r="M17" s="31"/>
-      <c r="N17" s="32"/>
-      <c r="O17" s="29"/>
-      <c r="P17" s="30"/>
-      <c r="Q17" s="30"/>
-      <c r="R17" s="30"/>
-      <c r="S17" s="30"/>
-      <c r="T17" s="30"/>
-      <c r="U17" s="30"/>
-      <c r="V17" s="30"/>
-      <c r="W17" s="33"/>
-      <c r="X17" s="34"/>
+      <c r="D17" s="79"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="30"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="29"/>
+      <c r="L17" s="29"/>
+      <c r="M17" s="30"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="28"/>
+      <c r="P17" s="29"/>
+      <c r="Q17" s="29"/>
+      <c r="R17" s="29"/>
+      <c r="S17" s="29"/>
+      <c r="T17" s="29"/>
+      <c r="U17" s="29"/>
+      <c r="V17" s="29"/>
+      <c r="W17" s="63" t="s">
+        <v>71</v>
+      </c>
+      <c r="X17" s="32"/>
       <c r="Y17" s="7"/>
       <c r="Z17"/>
     </row>
@@ -2568,119 +2636,119 @@
     </row>
     <row r="19" spans="1:27" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B19" s="22"/>
-      <c r="C19" s="72" t="s">
+      <c r="C19" s="104" t="s">
         <v>34</v>
       </c>
-      <c r="D19" s="73"/>
-      <c r="E19" s="73"/>
-      <c r="F19" s="73"/>
-      <c r="G19" s="73"/>
-      <c r="H19" s="73"/>
-      <c r="I19" s="73"/>
-      <c r="J19" s="73"/>
-      <c r="L19" s="61"/>
-      <c r="M19" s="60"/>
-      <c r="N19" s="63" t="s">
+      <c r="D19" s="105"/>
+      <c r="E19" s="105"/>
+      <c r="F19" s="105"/>
+      <c r="G19" s="105"/>
+      <c r="H19" s="105"/>
+      <c r="I19" s="105"/>
+      <c r="J19" s="105"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="56"/>
+      <c r="N19" s="59" t="s">
         <v>60</v>
       </c>
-      <c r="O19" s="60"/>
-      <c r="P19" s="62"/>
-      <c r="Q19" s="56" t="s">
+      <c r="O19" s="56"/>
+      <c r="P19" s="58"/>
+      <c r="Q19" s="52" t="s">
         <v>53</v>
       </c>
       <c r="AA19" s="10"/>
     </row>
     <row r="20" spans="1:27" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="M20" s="51" t="s">
+      <c r="M20" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="N20" s="52" t="s">
+      <c r="N20" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="O20" s="53" t="s">
+      <c r="O20" s="49" t="s">
         <v>62</v>
       </c>
-      <c r="Q20" s="56" t="s">
+      <c r="Q20" s="52" t="s">
         <v>54</v>
       </c>
       <c r="AA20" s="10"/>
     </row>
     <row r="21" spans="1:27" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="24"/>
-      <c r="C21" s="72" t="s">
+      <c r="C21" s="104" t="s">
         <v>39</v>
       </c>
-      <c r="D21" s="73"/>
-      <c r="E21" s="73"/>
-      <c r="F21" s="73"/>
-      <c r="G21" s="73"/>
-      <c r="H21" s="73"/>
-      <c r="I21" s="73"/>
-      <c r="J21" s="73"/>
-      <c r="M21" s="83" t="s">
+      <c r="D21" s="105"/>
+      <c r="E21" s="105"/>
+      <c r="F21" s="105"/>
+      <c r="G21" s="105"/>
+      <c r="H21" s="105"/>
+      <c r="I21" s="105"/>
+      <c r="J21" s="105"/>
+      <c r="M21" s="112" t="s">
         <v>63</v>
       </c>
-      <c r="N21" s="113" t="s">
+      <c r="N21" s="66" t="s">
         <v>63</v>
       </c>
-      <c r="O21" s="115" t="s">
+      <c r="O21" s="68" t="s">
         <v>63</v>
       </c>
       <c r="Q21"/>
       <c r="AA21" s="10"/>
     </row>
     <row r="22" spans="1:27" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C22" s="54"/>
-      <c r="D22" s="54"/>
-      <c r="E22" s="54"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="54"/>
-      <c r="H22" s="55"/>
-      <c r="I22" s="55"/>
-      <c r="J22" s="55"/>
-      <c r="M22" s="84"/>
-      <c r="N22" s="114"/>
-      <c r="O22" s="116"/>
-      <c r="Q22" s="56" t="s">
+      <c r="C22" s="50"/>
+      <c r="D22" s="50"/>
+      <c r="E22" s="50"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="50"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="51"/>
+      <c r="J22" s="51"/>
+      <c r="M22" s="113"/>
+      <c r="N22" s="67"/>
+      <c r="O22" s="69"/>
+      <c r="Q22" s="52" t="s">
         <v>55</v>
       </c>
       <c r="AA22" s="10"/>
     </row>
     <row r="23" spans="1:27" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="23"/>
-      <c r="C23" s="72" t="s">
+      <c r="C23" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="D23" s="73"/>
-      <c r="E23" s="73"/>
-      <c r="F23" s="73"/>
-      <c r="G23" s="73"/>
-      <c r="H23" s="73"/>
-      <c r="I23" s="73"/>
-      <c r="J23" s="73"/>
-      <c r="K23" s="56"/>
-      <c r="M23" s="117" t="s">
+      <c r="D23" s="105"/>
+      <c r="E23" s="105"/>
+      <c r="F23" s="105"/>
+      <c r="G23" s="105"/>
+      <c r="H23" s="105"/>
+      <c r="I23" s="105"/>
+      <c r="J23" s="105"/>
+      <c r="K23" s="52"/>
+      <c r="M23" s="70" t="s">
         <v>35</v>
       </c>
-      <c r="N23" s="119" t="s">
+      <c r="N23" s="72" t="s">
         <v>36</v>
       </c>
-      <c r="O23" s="117" t="s">
+      <c r="O23" s="70" t="s">
         <v>37</v>
       </c>
       <c r="AA23" s="10"/>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="K24" s="56"/>
+      <c r="K24" s="52"/>
       <c r="L24"/>
-      <c r="M24" s="118"/>
-      <c r="N24" s="118"/>
-      <c r="O24" s="118"/>
+      <c r="M24" s="71"/>
+      <c r="N24" s="71"/>
+      <c r="O24" s="71"/>
       <c r="P24"/>
       <c r="AA24" s="10"/>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="K25" s="56"/>
+      <c r="K25" s="52"/>
       <c r="L25"/>
       <c r="P25"/>
       <c r="Q25"/>
@@ -2688,31 +2756,6 @@
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="N21:N22"/>
-    <mergeCell ref="O21:O22"/>
-    <mergeCell ref="M23:M24"/>
-    <mergeCell ref="N23:N24"/>
-    <mergeCell ref="O23:O24"/>
-    <mergeCell ref="B12:B17"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="X4:X7"/>
-    <mergeCell ref="O4:O7"/>
-    <mergeCell ref="S4:S7"/>
-    <mergeCell ref="P4:P7"/>
-    <mergeCell ref="Q4:Q7"/>
-    <mergeCell ref="R4:R7"/>
-    <mergeCell ref="T4:T7"/>
-    <mergeCell ref="V4:V7"/>
     <mergeCell ref="C21:J21"/>
     <mergeCell ref="C23:J23"/>
     <mergeCell ref="U4:U7"/>
@@ -2729,6 +2772,31 @@
     <mergeCell ref="H4:H7"/>
     <mergeCell ref="I4:I7"/>
     <mergeCell ref="M21:M22"/>
+    <mergeCell ref="X4:X7"/>
+    <mergeCell ref="O4:O7"/>
+    <mergeCell ref="S4:S7"/>
+    <mergeCell ref="P4:P7"/>
+    <mergeCell ref="Q4:Q7"/>
+    <mergeCell ref="R4:R7"/>
+    <mergeCell ref="T4:T7"/>
+    <mergeCell ref="V4:V7"/>
+    <mergeCell ref="B12:B17"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="N21:N22"/>
+    <mergeCell ref="O21:O22"/>
+    <mergeCell ref="M23:M24"/>
+    <mergeCell ref="N23:N24"/>
+    <mergeCell ref="O23:O24"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2746,351 +2814,351 @@
   <sheetData>
     <row r="1" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B2" s="120" t="s">
+      <c r="B2" s="114" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="120"/>
-      <c r="D2" s="120"/>
-      <c r="E2" s="120"/>
-      <c r="F2" s="120"/>
-      <c r="G2" s="120"/>
-      <c r="H2" s="120"/>
-      <c r="I2" s="120"/>
-      <c r="J2" s="120"/>
-      <c r="K2" s="120"/>
-      <c r="L2" s="120"/>
-      <c r="M2" s="120"/>
-      <c r="N2" s="120"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
+      <c r="I2" s="114"/>
+      <c r="J2" s="114"/>
+      <c r="K2" s="114"/>
+      <c r="L2" s="114"/>
+      <c r="M2" s="114"/>
+      <c r="N2" s="114"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B3" s="121"/>
-      <c r="C3" s="121"/>
-      <c r="D3" s="121"/>
-      <c r="E3" s="121"/>
-      <c r="F3" s="121"/>
-      <c r="G3" s="121"/>
-      <c r="H3" s="121"/>
-      <c r="I3" s="121"/>
-      <c r="J3" s="121"/>
-      <c r="K3" s="121"/>
-      <c r="L3" s="121"/>
-      <c r="M3" s="121"/>
-      <c r="N3" s="121"/>
+      <c r="B3" s="115"/>
+      <c r="C3" s="115"/>
+      <c r="D3" s="115"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="115"/>
+      <c r="H3" s="115"/>
+      <c r="I3" s="115"/>
+      <c r="J3" s="115"/>
+      <c r="K3" s="115"/>
+      <c r="L3" s="115"/>
+      <c r="M3" s="115"/>
+      <c r="N3" s="115"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B4" s="121"/>
-      <c r="C4" s="121"/>
-      <c r="D4" s="121"/>
-      <c r="E4" s="121"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121"/>
-      <c r="I4" s="121"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="121"/>
-      <c r="L4" s="121"/>
-      <c r="M4" s="121"/>
-      <c r="N4" s="121"/>
+      <c r="B4" s="115"/>
+      <c r="C4" s="115"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="115"/>
+      <c r="L4" s="115"/>
+      <c r="M4" s="115"/>
+      <c r="N4" s="115"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B5" s="121"/>
-      <c r="C5" s="121"/>
-      <c r="D5" s="121"/>
-      <c r="E5" s="121"/>
-      <c r="F5" s="121"/>
-      <c r="G5" s="121"/>
-      <c r="H5" s="121"/>
-      <c r="I5" s="121"/>
-      <c r="J5" s="121"/>
-      <c r="K5" s="121"/>
-      <c r="L5" s="121"/>
-      <c r="M5" s="121"/>
-      <c r="N5" s="121"/>
+      <c r="B5" s="115"/>
+      <c r="C5" s="115"/>
+      <c r="D5" s="115"/>
+      <c r="E5" s="115"/>
+      <c r="F5" s="115"/>
+      <c r="G5" s="115"/>
+      <c r="H5" s="115"/>
+      <c r="I5" s="115"/>
+      <c r="J5" s="115"/>
+      <c r="K5" s="115"/>
+      <c r="L5" s="115"/>
+      <c r="M5" s="115"/>
+      <c r="N5" s="115"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B6" s="121"/>
-      <c r="C6" s="121"/>
-      <c r="D6" s="121"/>
-      <c r="E6" s="121"/>
-      <c r="F6" s="121"/>
-      <c r="G6" s="121"/>
-      <c r="H6" s="121"/>
-      <c r="I6" s="121"/>
-      <c r="J6" s="121"/>
-      <c r="K6" s="121"/>
-      <c r="L6" s="121"/>
-      <c r="M6" s="121"/>
-      <c r="N6" s="121"/>
+      <c r="B6" s="115"/>
+      <c r="C6" s="115"/>
+      <c r="D6" s="115"/>
+      <c r="E6" s="115"/>
+      <c r="F6" s="115"/>
+      <c r="G6" s="115"/>
+      <c r="H6" s="115"/>
+      <c r="I6" s="115"/>
+      <c r="J6" s="115"/>
+      <c r="K6" s="115"/>
+      <c r="L6" s="115"/>
+      <c r="M6" s="115"/>
+      <c r="N6" s="115"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B7" s="121"/>
-      <c r="C7" s="121"/>
-      <c r="D7" s="121"/>
-      <c r="E7" s="121"/>
-      <c r="F7" s="121"/>
-      <c r="G7" s="121"/>
-      <c r="H7" s="121"/>
-      <c r="I7" s="121"/>
-      <c r="J7" s="121"/>
-      <c r="K7" s="121"/>
-      <c r="L7" s="121"/>
-      <c r="M7" s="121"/>
-      <c r="N7" s="121"/>
+      <c r="B7" s="115"/>
+      <c r="C7" s="115"/>
+      <c r="D7" s="115"/>
+      <c r="E7" s="115"/>
+      <c r="F7" s="115"/>
+      <c r="G7" s="115"/>
+      <c r="H7" s="115"/>
+      <c r="I7" s="115"/>
+      <c r="J7" s="115"/>
+      <c r="K7" s="115"/>
+      <c r="L7" s="115"/>
+      <c r="M7" s="115"/>
+      <c r="N7" s="115"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B8" s="121"/>
-      <c r="C8" s="121"/>
-      <c r="D8" s="121"/>
-      <c r="E8" s="121"/>
-      <c r="F8" s="121"/>
-      <c r="G8" s="121"/>
-      <c r="H8" s="121"/>
-      <c r="I8" s="121"/>
-      <c r="J8" s="121"/>
-      <c r="K8" s="121"/>
-      <c r="L8" s="121"/>
-      <c r="M8" s="121"/>
-      <c r="N8" s="121"/>
+      <c r="B8" s="115"/>
+      <c r="C8" s="115"/>
+      <c r="D8" s="115"/>
+      <c r="E8" s="115"/>
+      <c r="F8" s="115"/>
+      <c r="G8" s="115"/>
+      <c r="H8" s="115"/>
+      <c r="I8" s="115"/>
+      <c r="J8" s="115"/>
+      <c r="K8" s="115"/>
+      <c r="L8" s="115"/>
+      <c r="M8" s="115"/>
+      <c r="N8" s="115"/>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B9" s="121"/>
-      <c r="C9" s="121"/>
-      <c r="D9" s="121"/>
-      <c r="E9" s="121"/>
-      <c r="F9" s="121"/>
-      <c r="G9" s="121"/>
-      <c r="H9" s="121"/>
-      <c r="I9" s="121"/>
-      <c r="J9" s="121"/>
-      <c r="K9" s="121"/>
-      <c r="L9" s="121"/>
-      <c r="M9" s="121"/>
-      <c r="N9" s="121"/>
+      <c r="B9" s="115"/>
+      <c r="C9" s="115"/>
+      <c r="D9" s="115"/>
+      <c r="E9" s="115"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="115"/>
+      <c r="H9" s="115"/>
+      <c r="I9" s="115"/>
+      <c r="J9" s="115"/>
+      <c r="K9" s="115"/>
+      <c r="L9" s="115"/>
+      <c r="M9" s="115"/>
+      <c r="N9" s="115"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B10" s="121"/>
-      <c r="C10" s="121"/>
-      <c r="D10" s="121"/>
-      <c r="E10" s="121"/>
-      <c r="F10" s="121"/>
-      <c r="G10" s="121"/>
-      <c r="H10" s="121"/>
-      <c r="I10" s="121"/>
-      <c r="J10" s="121"/>
-      <c r="K10" s="121"/>
-      <c r="L10" s="121"/>
-      <c r="M10" s="121"/>
-      <c r="N10" s="121"/>
+      <c r="B10" s="115"/>
+      <c r="C10" s="115"/>
+      <c r="D10" s="115"/>
+      <c r="E10" s="115"/>
+      <c r="F10" s="115"/>
+      <c r="G10" s="115"/>
+      <c r="H10" s="115"/>
+      <c r="I10" s="115"/>
+      <c r="J10" s="115"/>
+      <c r="K10" s="115"/>
+      <c r="L10" s="115"/>
+      <c r="M10" s="115"/>
+      <c r="N10" s="115"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B11" s="121"/>
-      <c r="C11" s="121"/>
-      <c r="D11" s="121"/>
-      <c r="E11" s="121"/>
-      <c r="F11" s="121"/>
-      <c r="G11" s="121"/>
-      <c r="H11" s="121"/>
-      <c r="I11" s="121"/>
-      <c r="J11" s="121"/>
-      <c r="K11" s="121"/>
-      <c r="L11" s="121"/>
-      <c r="M11" s="121"/>
-      <c r="N11" s="121"/>
+      <c r="B11" s="115"/>
+      <c r="C11" s="115"/>
+      <c r="D11" s="115"/>
+      <c r="E11" s="115"/>
+      <c r="F11" s="115"/>
+      <c r="G11" s="115"/>
+      <c r="H11" s="115"/>
+      <c r="I11" s="115"/>
+      <c r="J11" s="115"/>
+      <c r="K11" s="115"/>
+      <c r="L11" s="115"/>
+      <c r="M11" s="115"/>
+      <c r="N11" s="115"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B12" s="121"/>
-      <c r="C12" s="121"/>
-      <c r="D12" s="121"/>
-      <c r="E12" s="121"/>
-      <c r="F12" s="121"/>
-      <c r="G12" s="121"/>
-      <c r="H12" s="121"/>
-      <c r="I12" s="121"/>
-      <c r="J12" s="121"/>
-      <c r="K12" s="121"/>
-      <c r="L12" s="121"/>
-      <c r="M12" s="121"/>
-      <c r="N12" s="121"/>
+      <c r="B12" s="115"/>
+      <c r="C12" s="115"/>
+      <c r="D12" s="115"/>
+      <c r="E12" s="115"/>
+      <c r="F12" s="115"/>
+      <c r="G12" s="115"/>
+      <c r="H12" s="115"/>
+      <c r="I12" s="115"/>
+      <c r="J12" s="115"/>
+      <c r="K12" s="115"/>
+      <c r="L12" s="115"/>
+      <c r="M12" s="115"/>
+      <c r="N12" s="115"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B13" s="121"/>
-      <c r="C13" s="121"/>
-      <c r="D13" s="121"/>
-      <c r="E13" s="121"/>
-      <c r="F13" s="121"/>
-      <c r="G13" s="121"/>
-      <c r="H13" s="121"/>
-      <c r="I13" s="121"/>
-      <c r="J13" s="121"/>
-      <c r="K13" s="121"/>
-      <c r="L13" s="121"/>
-      <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
+      <c r="B13" s="115"/>
+      <c r="C13" s="115"/>
+      <c r="D13" s="115"/>
+      <c r="E13" s="115"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="115"/>
+      <c r="H13" s="115"/>
+      <c r="I13" s="115"/>
+      <c r="J13" s="115"/>
+      <c r="K13" s="115"/>
+      <c r="L13" s="115"/>
+      <c r="M13" s="115"/>
+      <c r="N13" s="115"/>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B14" s="121"/>
-      <c r="C14" s="121"/>
-      <c r="D14" s="121"/>
-      <c r="E14" s="121"/>
-      <c r="F14" s="121"/>
-      <c r="G14" s="121"/>
-      <c r="H14" s="121"/>
-      <c r="I14" s="121"/>
-      <c r="J14" s="121"/>
-      <c r="K14" s="121"/>
-      <c r="L14" s="121"/>
-      <c r="M14" s="121"/>
-      <c r="N14" s="121"/>
+      <c r="B14" s="115"/>
+      <c r="C14" s="115"/>
+      <c r="D14" s="115"/>
+      <c r="E14" s="115"/>
+      <c r="F14" s="115"/>
+      <c r="G14" s="115"/>
+      <c r="H14" s="115"/>
+      <c r="I14" s="115"/>
+      <c r="J14" s="115"/>
+      <c r="K14" s="115"/>
+      <c r="L14" s="115"/>
+      <c r="M14" s="115"/>
+      <c r="N14" s="115"/>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B15" s="121"/>
-      <c r="C15" s="121"/>
-      <c r="D15" s="121"/>
-      <c r="E15" s="121"/>
-      <c r="F15" s="121"/>
-      <c r="G15" s="121"/>
-      <c r="H15" s="121"/>
-      <c r="I15" s="121"/>
-      <c r="J15" s="121"/>
-      <c r="K15" s="121"/>
-      <c r="L15" s="121"/>
-      <c r="M15" s="121"/>
-      <c r="N15" s="121"/>
+      <c r="B15" s="115"/>
+      <c r="C15" s="115"/>
+      <c r="D15" s="115"/>
+      <c r="E15" s="115"/>
+      <c r="F15" s="115"/>
+      <c r="G15" s="115"/>
+      <c r="H15" s="115"/>
+      <c r="I15" s="115"/>
+      <c r="J15" s="115"/>
+      <c r="K15" s="115"/>
+      <c r="L15" s="115"/>
+      <c r="M15" s="115"/>
+      <c r="N15" s="115"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B16" s="121"/>
-      <c r="C16" s="121"/>
-      <c r="D16" s="121"/>
-      <c r="E16" s="121"/>
-      <c r="F16" s="121"/>
-      <c r="G16" s="121"/>
-      <c r="H16" s="121"/>
-      <c r="I16" s="121"/>
-      <c r="J16" s="121"/>
-      <c r="K16" s="121"/>
-      <c r="L16" s="121"/>
-      <c r="M16" s="121"/>
-      <c r="N16" s="121"/>
+      <c r="B16" s="115"/>
+      <c r="C16" s="115"/>
+      <c r="D16" s="115"/>
+      <c r="E16" s="115"/>
+      <c r="F16" s="115"/>
+      <c r="G16" s="115"/>
+      <c r="H16" s="115"/>
+      <c r="I16" s="115"/>
+      <c r="J16" s="115"/>
+      <c r="K16" s="115"/>
+      <c r="L16" s="115"/>
+      <c r="M16" s="115"/>
+      <c r="N16" s="115"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B17" s="121"/>
-      <c r="C17" s="121"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="121"/>
-      <c r="G17" s="121"/>
-      <c r="H17" s="121"/>
-      <c r="I17" s="121"/>
-      <c r="J17" s="121"/>
-      <c r="K17" s="121"/>
-      <c r="L17" s="121"/>
-      <c r="M17" s="121"/>
-      <c r="N17" s="121"/>
+      <c r="B17" s="115"/>
+      <c r="C17" s="115"/>
+      <c r="D17" s="115"/>
+      <c r="E17" s="115"/>
+      <c r="F17" s="115"/>
+      <c r="G17" s="115"/>
+      <c r="H17" s="115"/>
+      <c r="I17" s="115"/>
+      <c r="J17" s="115"/>
+      <c r="K17" s="115"/>
+      <c r="L17" s="115"/>
+      <c r="M17" s="115"/>
+      <c r="N17" s="115"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B18" s="121"/>
-      <c r="C18" s="121"/>
-      <c r="D18" s="121"/>
-      <c r="E18" s="121"/>
-      <c r="F18" s="121"/>
-      <c r="G18" s="121"/>
-      <c r="H18" s="121"/>
-      <c r="I18" s="121"/>
-      <c r="J18" s="121"/>
-      <c r="K18" s="121"/>
-      <c r="L18" s="121"/>
-      <c r="M18" s="121"/>
-      <c r="N18" s="121"/>
+      <c r="B18" s="115"/>
+      <c r="C18" s="115"/>
+      <c r="D18" s="115"/>
+      <c r="E18" s="115"/>
+      <c r="F18" s="115"/>
+      <c r="G18" s="115"/>
+      <c r="H18" s="115"/>
+      <c r="I18" s="115"/>
+      <c r="J18" s="115"/>
+      <c r="K18" s="115"/>
+      <c r="L18" s="115"/>
+      <c r="M18" s="115"/>
+      <c r="N18" s="115"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B19" s="121"/>
-      <c r="C19" s="121"/>
-      <c r="D19" s="121"/>
-      <c r="E19" s="121"/>
-      <c r="F19" s="121"/>
-      <c r="G19" s="121"/>
-      <c r="H19" s="121"/>
-      <c r="I19" s="121"/>
-      <c r="J19" s="121"/>
-      <c r="K19" s="121"/>
-      <c r="L19" s="121"/>
-      <c r="M19" s="121"/>
-      <c r="N19" s="121"/>
+      <c r="B19" s="115"/>
+      <c r="C19" s="115"/>
+      <c r="D19" s="115"/>
+      <c r="E19" s="115"/>
+      <c r="F19" s="115"/>
+      <c r="G19" s="115"/>
+      <c r="H19" s="115"/>
+      <c r="I19" s="115"/>
+      <c r="J19" s="115"/>
+      <c r="K19" s="115"/>
+      <c r="L19" s="115"/>
+      <c r="M19" s="115"/>
+      <c r="N19" s="115"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B20" s="121"/>
-      <c r="C20" s="121"/>
-      <c r="D20" s="121"/>
-      <c r="E20" s="121"/>
-      <c r="F20" s="121"/>
-      <c r="G20" s="121"/>
-      <c r="H20" s="121"/>
-      <c r="I20" s="121"/>
-      <c r="J20" s="121"/>
-      <c r="K20" s="121"/>
-      <c r="L20" s="121"/>
-      <c r="M20" s="121"/>
-      <c r="N20" s="121"/>
+      <c r="B20" s="115"/>
+      <c r="C20" s="115"/>
+      <c r="D20" s="115"/>
+      <c r="E20" s="115"/>
+      <c r="F20" s="115"/>
+      <c r="G20" s="115"/>
+      <c r="H20" s="115"/>
+      <c r="I20" s="115"/>
+      <c r="J20" s="115"/>
+      <c r="K20" s="115"/>
+      <c r="L20" s="115"/>
+      <c r="M20" s="115"/>
+      <c r="N20" s="115"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B21" s="121"/>
-      <c r="C21" s="121"/>
-      <c r="D21" s="121"/>
-      <c r="E21" s="121"/>
-      <c r="F21" s="121"/>
-      <c r="G21" s="121"/>
-      <c r="H21" s="121"/>
-      <c r="I21" s="121"/>
-      <c r="J21" s="121"/>
-      <c r="K21" s="121"/>
-      <c r="L21" s="121"/>
-      <c r="M21" s="121"/>
-      <c r="N21" s="121"/>
+      <c r="B21" s="115"/>
+      <c r="C21" s="115"/>
+      <c r="D21" s="115"/>
+      <c r="E21" s="115"/>
+      <c r="F21" s="115"/>
+      <c r="G21" s="115"/>
+      <c r="H21" s="115"/>
+      <c r="I21" s="115"/>
+      <c r="J21" s="115"/>
+      <c r="K21" s="115"/>
+      <c r="L21" s="115"/>
+      <c r="M21" s="115"/>
+      <c r="N21" s="115"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B22" s="121"/>
-      <c r="C22" s="121"/>
-      <c r="D22" s="121"/>
-      <c r="E22" s="121"/>
-      <c r="F22" s="121"/>
-      <c r="G22" s="121"/>
-      <c r="H22" s="121"/>
-      <c r="I22" s="121"/>
-      <c r="J22" s="121"/>
-      <c r="K22" s="121"/>
-      <c r="L22" s="121"/>
-      <c r="M22" s="121"/>
-      <c r="N22" s="121"/>
+      <c r="B22" s="115"/>
+      <c r="C22" s="115"/>
+      <c r="D22" s="115"/>
+      <c r="E22" s="115"/>
+      <c r="F22" s="115"/>
+      <c r="G22" s="115"/>
+      <c r="H22" s="115"/>
+      <c r="I22" s="115"/>
+      <c r="J22" s="115"/>
+      <c r="K22" s="115"/>
+      <c r="L22" s="115"/>
+      <c r="M22" s="115"/>
+      <c r="N22" s="115"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B23" s="121"/>
-      <c r="C23" s="121"/>
-      <c r="D23" s="121"/>
-      <c r="E23" s="121"/>
-      <c r="F23" s="121"/>
-      <c r="G23" s="121"/>
-      <c r="H23" s="121"/>
-      <c r="I23" s="121"/>
-      <c r="J23" s="121"/>
-      <c r="K23" s="121"/>
-      <c r="L23" s="121"/>
-      <c r="M23" s="121"/>
-      <c r="N23" s="121"/>
+      <c r="B23" s="115"/>
+      <c r="C23" s="115"/>
+      <c r="D23" s="115"/>
+      <c r="E23" s="115"/>
+      <c r="F23" s="115"/>
+      <c r="G23" s="115"/>
+      <c r="H23" s="115"/>
+      <c r="I23" s="115"/>
+      <c r="J23" s="115"/>
+      <c r="K23" s="115"/>
+      <c r="L23" s="115"/>
+      <c r="M23" s="115"/>
+      <c r="N23" s="115"/>
     </row>
     <row r="24" spans="2:14" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="121"/>
-      <c r="C24" s="121"/>
-      <c r="D24" s="121"/>
-      <c r="E24" s="121"/>
-      <c r="F24" s="121"/>
-      <c r="G24" s="121"/>
-      <c r="H24" s="121"/>
-      <c r="I24" s="121"/>
-      <c r="J24" s="121"/>
-      <c r="K24" s="121"/>
-      <c r="L24" s="121"/>
-      <c r="M24" s="121"/>
-      <c r="N24" s="121"/>
+      <c r="B24" s="115"/>
+      <c r="C24" s="115"/>
+      <c r="D24" s="115"/>
+      <c r="E24" s="115"/>
+      <c r="F24" s="115"/>
+      <c r="G24" s="115"/>
+      <c r="H24" s="115"/>
+      <c r="I24" s="115"/>
+      <c r="J24" s="115"/>
+      <c r="K24" s="115"/>
+      <c r="L24" s="115"/>
+      <c r="M24" s="115"/>
+      <c r="N24" s="115"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3372,15 +3440,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="cc018f0f-33de-4c4c-920d-26dc6e1acc33" xsi:nil="true"/>
@@ -3391,6 +3450,15 @@
     <Description xmlns="8e39aab0-005d-45b6-a80e-05e5df2908d1" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3413,14 +3481,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FEB2382-117C-4B02-B61B-7207F73C69D2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA41F33-D73A-4946-89E5-437EF57CC713}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -3435,4 +3495,12 @@
     <ds:schemaRef ds:uri="8e39aab0-005d-45b6-a80e-05e5df2908d1"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FEB2382-117C-4B02-B61B-7207F73C69D2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>